--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\00- EELU\Advising Data\advisor-finder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9FFB65-85A6-448D-BF5D-A976BC4CB0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF2FC8D-5598-4769-9687-AF01A2D87137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1815" windowWidth="29040" windowHeight="15720" xr2:uid="{1912A759-5108-4608-88A6-33A8F4C2828A}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="549">
   <si>
     <t>Student ID</t>
   </si>
@@ -1473,6 +1473,222 @@
   </si>
   <si>
     <t>eshaban@eelu.edu.eg</t>
+  </si>
+  <si>
+    <t>أحمد عبد العظيم عبد العظيم محمد</t>
+  </si>
+  <si>
+    <t>أحمد محمد أحمد حسن خليفة</t>
+  </si>
+  <si>
+    <t>أمل أحمد محمد عنتر</t>
+  </si>
+  <si>
+    <t>ابراهيم اسامة عبدالستار السيد</t>
+  </si>
+  <si>
+    <t>احمد أسامة عبدالوهاب عبدالعزيز</t>
+  </si>
+  <si>
+    <t>احمد على حفنى على</t>
+  </si>
+  <si>
+    <t>احمد نبيل عويس القرنى صابر</t>
+  </si>
+  <si>
+    <t>امنية ابو العز زيدان محجوب</t>
+  </si>
+  <si>
+    <t>ايه مختار احمد شحات</t>
+  </si>
+  <si>
+    <t>بثينه عويس عجمي محمد</t>
+  </si>
+  <si>
+    <t>بسملة اسماعيل أحمد جمعه</t>
+  </si>
+  <si>
+    <t>بسملة ربيع عبدالله محمد</t>
+  </si>
+  <si>
+    <t>بسملة شعبان يونس على</t>
+  </si>
+  <si>
+    <t>بسمله محمد رمضان معروف</t>
+  </si>
+  <si>
+    <t>بسمله محمود عبد الرازق جاد</t>
+  </si>
+  <si>
+    <t>تقوى أشرف السيد رمضان</t>
+  </si>
+  <si>
+    <t>جنا أحمد عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>جنه عمادالدين احمد عبدالوهاب</t>
+  </si>
+  <si>
+    <t>جنى على حامد بدوى</t>
+  </si>
+  <si>
+    <t>جنى مجدى الحسينى عبدالعظيم</t>
+  </si>
+  <si>
+    <t>خالد اشرف فتحي عبدالمقصود غنيم</t>
+  </si>
+  <si>
+    <t>خالد محمد عبدالوهاب عطا</t>
+  </si>
+  <si>
+    <t>داليا مصطفى معبد محمد</t>
+  </si>
+  <si>
+    <t>دميانه كرم يوسف سليمان قريوس</t>
+  </si>
+  <si>
+    <t>رؤى محمد عبدالمنعم عبده</t>
+  </si>
+  <si>
+    <t>ريهام احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>زمزم فرج رجب عبد ربه</t>
+  </si>
+  <si>
+    <t>زهور علاء محمد خليفة</t>
+  </si>
+  <si>
+    <t>زياد هيثم ابراهيم كامل</t>
+  </si>
+  <si>
+    <t>زياد وليد محمد محمد عبدالجواد</t>
+  </si>
+  <si>
+    <t>زينب حسن عبدالوهاب محمد السيد</t>
+  </si>
+  <si>
+    <t>ساره احمد ميهوب عبدالكريم</t>
+  </si>
+  <si>
+    <t>ساره علي حموده محمد</t>
+  </si>
+  <si>
+    <t>ساره محمد محمود حسن</t>
+  </si>
+  <si>
+    <t>ساندرا ايليا عبدالملاك توفيق سليمان</t>
+  </si>
+  <si>
+    <t>سجى عبدالفتاح عبدالهادى احمد</t>
+  </si>
+  <si>
+    <t>سما ساهر سعيد حسين</t>
+  </si>
+  <si>
+    <t>سما محمد سعيد احمد</t>
+  </si>
+  <si>
+    <t>شادي علي محمد قطب</t>
+  </si>
+  <si>
+    <t>شروق عادل رمضان عبدالحفيظ</t>
+  </si>
+  <si>
+    <t>شريف كمال محمد فوزى موسى</t>
+  </si>
+  <si>
+    <t>شهاب الدين بلال عبد البديع نايل</t>
+  </si>
+  <si>
+    <t>شهد أشرف السيد رمضان منصور</t>
+  </si>
+  <si>
+    <t>شوقي هاني شوقي ميخائيل</t>
+  </si>
+  <si>
+    <t>طارق مصطفى محمد عبد الغنى</t>
+  </si>
+  <si>
+    <t>عبد الرحمن ناجي محمد نبيل</t>
+  </si>
+  <si>
+    <t>عمرو فرج على عيد</t>
+  </si>
+  <si>
+    <t>عمرو محمد محمد علي</t>
+  </si>
+  <si>
+    <t>عمرو محمود محمود محمد</t>
+  </si>
+  <si>
+    <t>فادي ايمن ميلاد يونان</t>
+  </si>
+  <si>
+    <t>فارس أحمد على ابراهيم طلبه</t>
+  </si>
+  <si>
+    <t>فاطمه ربيع شعبان محمد</t>
+  </si>
+  <si>
+    <t>فدوي محمد حسين محمد</t>
+  </si>
+  <si>
+    <t>كارولين توبه عبده ابراهيم</t>
+  </si>
+  <si>
+    <t>كارين اشرف فايز زكي</t>
+  </si>
+  <si>
+    <t>كيرليس سمير غطاس غبريال</t>
+  </si>
+  <si>
+    <t>ماريا عاطف رياض زكى</t>
+  </si>
+  <si>
+    <t>ماريا لبيب عبدالمسيح لبيب</t>
+  </si>
+  <si>
+    <t>مازن وليد سامى أحمد</t>
+  </si>
+  <si>
+    <t>محمد احمد حمدي محمد</t>
+  </si>
+  <si>
+    <t>محمد احمد رمضان احمد</t>
+  </si>
+  <si>
+    <t>محمد محمود سيد الدامي</t>
+  </si>
+  <si>
+    <t>محمد مصطفى رمضان عبدالجيد</t>
+  </si>
+  <si>
+    <t>مصطفى محمود رمضان سيد</t>
+  </si>
+  <si>
+    <t>معتز على سعيد ابوبكر</t>
+  </si>
+  <si>
+    <t>ندا اشرف سعد محمد</t>
+  </si>
+  <si>
+    <t>ندى احمد شوقي عبدالسميع احمد</t>
+  </si>
+  <si>
+    <t>ندى ربيع أحمد السيد</t>
+  </si>
+  <si>
+    <t>ندى يوسف حجاج حسن</t>
+  </si>
+  <si>
+    <t>نرمين عبد التواب حسن جمعه</t>
+  </si>
+  <si>
+    <t>د. تسبيح إيهاب</t>
+  </si>
+  <si>
+    <t>tihababdelaziz@eelu.edu.eg</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507AC9FC-3305-4A8E-963E-423E46E70006}">
-  <dimension ref="A1:D462"/>
+  <dimension ref="A1:D532"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
@@ -8335,6 +8551,986 @@
       </c>
       <c r="D462" s="2" t="s">
         <v>476</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A463" s="1">
+        <v>2403060</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C463" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D463" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A464" s="1">
+        <v>2200435</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C464" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D464" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A465" s="1">
+        <v>2401854</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C465" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D465" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A466" s="1">
+        <v>2403334</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C466" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D466" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A467" s="1">
+        <v>2400598</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C467" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D467" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A468" s="1">
+        <v>2402867</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C468" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D468" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A469" s="1">
+        <v>2402168</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C469" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D469" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A470" s="1">
+        <v>2403847</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D470" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A471" s="1">
+        <v>2402955</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D471" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A472" s="1">
+        <v>2402417</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C472" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D472" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A473" s="1">
+        <v>2402371</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D473" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A474" s="1">
+        <v>2403846</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C474" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D474" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A475" s="1">
+        <v>2402418</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D475" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A476" s="1">
+        <v>2403241</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A477" s="1">
+        <v>2403489</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D477" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A478" s="1">
+        <v>2403492</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C478" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D478" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A479" s="1">
+        <v>2400604</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D479" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A480" s="1">
+        <v>2403576</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D480" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A481" s="1">
+        <v>2402699</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D481" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A482" s="1">
+        <v>2402019</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D482" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A483" s="1">
+        <v>2401379</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D483" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A484" s="1">
+        <v>2400785</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D484" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A485" s="1">
+        <v>2400597</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C485" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D485" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A486" s="1">
+        <v>2400612</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C486" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D486" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A487" s="1">
+        <v>2403683</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C487" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D487" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A488" s="1">
+        <v>2402956</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C488" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D488" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A489" s="1">
+        <v>2403239</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C489" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D489" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A490" s="1">
+        <v>2402868</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D490" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A491" s="1">
+        <v>2200457</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C491" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D491" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A492" s="1">
+        <v>2400599</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C492" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D492" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A493" s="1">
+        <v>2401265</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C493" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D493" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A494" s="1">
+        <v>2403310</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C494" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D494" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A495" s="1">
+        <v>2203033</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C495" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D495" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A496" s="1">
+        <v>2400301</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C496" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D496" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A497" s="1">
+        <v>2402018</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C497" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A498" s="1">
+        <v>2403607</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C498" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D498" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A499" s="1">
+        <v>2200498</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C499" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D499" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A500" s="1">
+        <v>2403678</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C500" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D500" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A501" s="1">
+        <v>2403571</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C501" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D501" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A502" s="1">
+        <v>2200506</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C502" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D502" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A503" s="1">
+        <v>2403575</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C503" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D503" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A504" s="1">
+        <v>2402420</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C504" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D504" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A505" s="1">
+        <v>2200493</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D505" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A506" s="1">
+        <v>2403848</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C506" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D506" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A507" s="1">
+        <v>2200480</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D507" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A508" s="1">
+        <v>2401781</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C508" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D508" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A509" s="1">
+        <v>2402768</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D509" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A510" s="1">
+        <v>2303340</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C510" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D510" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A511" s="1">
+        <v>2301548</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C511" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D511" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A512" s="1">
+        <v>2402253</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C512" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D512" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A513" s="1">
+        <v>2303482</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D513" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A514" s="1">
+        <v>2403240</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D514" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A515" s="1">
+        <v>2400603</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C515" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D515" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A516" s="1">
+        <v>2402147</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C516" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D516" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A517" s="1">
+        <v>2300701</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D517" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A518" s="1">
+        <v>2302785</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C518" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D518" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A519" s="1">
+        <v>2400611</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C519" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D519" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A520" s="1">
+        <v>2303251</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D520" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A521" s="1">
+        <v>2303439</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C521" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D521" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A522" s="1">
+        <v>2403684</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D522" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A523" s="1">
+        <v>2403201</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D523" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A524" s="1">
+        <v>2202577</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D524" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A525" s="1">
+        <v>2200568</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D525" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A526" s="1">
+        <v>2200443</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D526" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A527" s="1">
+        <v>2200439</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D527" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A528" s="1">
+        <v>2200569</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D528" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A529" s="1">
+        <v>2200499</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C529" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D529" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A530" s="1">
+        <v>2202579</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C530" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D530" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A531" s="1">
+        <v>2200509</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C531" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D531" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A532" s="1">
+        <v>2200554</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C532" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D532" s="2" t="s">
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -8801,6 +9997,76 @@
     <hyperlink ref="D460" r:id="rId459" xr:uid="{C811E24C-5080-4561-AB97-439656D73078}"/>
     <hyperlink ref="D461" r:id="rId460" xr:uid="{AFAAD9B5-556D-4219-88B3-AE7EBC6B824D}"/>
     <hyperlink ref="D462" r:id="rId461" xr:uid="{E8E66896-B2F5-4A63-9038-70D92E5793DF}"/>
+    <hyperlink ref="D463" r:id="rId462" xr:uid="{06CE6014-3FBF-4007-A989-F89ECCF16B56}"/>
+    <hyperlink ref="D464" r:id="rId463" xr:uid="{8FB39E0B-4286-4A7E-B102-A9FC4AC6ED26}"/>
+    <hyperlink ref="D465" r:id="rId464" xr:uid="{696E7E97-76F4-4F8D-BB4E-1E33ECC2E35A}"/>
+    <hyperlink ref="D466" r:id="rId465" xr:uid="{67A1111E-DE97-41DB-B26A-636E40E0A692}"/>
+    <hyperlink ref="D467" r:id="rId466" xr:uid="{90C247A1-3FF0-4EA0-A0A0-EBB77BF07E38}"/>
+    <hyperlink ref="D468" r:id="rId467" xr:uid="{511D3D58-7B40-43CB-9FB7-93DFA69178A5}"/>
+    <hyperlink ref="D469" r:id="rId468" xr:uid="{35FF0E65-2D5F-46A2-A995-FF849E1D95AA}"/>
+    <hyperlink ref="D470" r:id="rId469" xr:uid="{76638A18-7F31-4721-BE7F-2622FED6343A}"/>
+    <hyperlink ref="D471" r:id="rId470" xr:uid="{02384410-25F4-461A-BEA2-511A1778016B}"/>
+    <hyperlink ref="D472" r:id="rId471" xr:uid="{21880536-9512-407A-A138-FF972D8CEDE9}"/>
+    <hyperlink ref="D473" r:id="rId472" xr:uid="{EF572E76-C8DF-48BC-970C-22E02099603D}"/>
+    <hyperlink ref="D474" r:id="rId473" xr:uid="{609D3004-6B35-4592-BCFF-F5EB1A0CC75B}"/>
+    <hyperlink ref="D475" r:id="rId474" xr:uid="{5363CCF8-2FBE-444F-98C0-AF1B6B6F8D53}"/>
+    <hyperlink ref="D476" r:id="rId475" xr:uid="{6164F5B3-6E9C-40EF-98BE-2102446D8E81}"/>
+    <hyperlink ref="D477" r:id="rId476" xr:uid="{B0E614BE-1CB4-4EA6-808F-E3CABE124570}"/>
+    <hyperlink ref="D478" r:id="rId477" xr:uid="{385628C5-567A-499A-B1C7-8E0CBC10C970}"/>
+    <hyperlink ref="D479" r:id="rId478" xr:uid="{0E86F95A-90E8-4C69-A72B-15B7956A7D0E}"/>
+    <hyperlink ref="D480" r:id="rId479" xr:uid="{21B148F1-8AA1-4E04-8549-30661F65BA6C}"/>
+    <hyperlink ref="D481" r:id="rId480" xr:uid="{0FB9398D-126F-4B7E-A03A-5A1B6A0C9C34}"/>
+    <hyperlink ref="D482" r:id="rId481" xr:uid="{8E725281-4800-4C65-9E8C-7E88AC50F081}"/>
+    <hyperlink ref="D483" r:id="rId482" xr:uid="{96F7DFFE-8D41-479D-9FC4-E5B39CFB68FD}"/>
+    <hyperlink ref="D484" r:id="rId483" xr:uid="{AA6790D1-56C3-4CE2-80CD-73143ED463A2}"/>
+    <hyperlink ref="D485" r:id="rId484" xr:uid="{A8436332-5DA5-4FBD-AAF9-7FB26A9B3F70}"/>
+    <hyperlink ref="D486" r:id="rId485" xr:uid="{AD8C325A-715E-4A6A-B10E-D201533D8094}"/>
+    <hyperlink ref="D487" r:id="rId486" xr:uid="{B8C86FDD-5FB6-40E6-B967-7F1ED90B542B}"/>
+    <hyperlink ref="D488" r:id="rId487" xr:uid="{257DF475-3317-4221-B2DC-ADC319D7C948}"/>
+    <hyperlink ref="D489" r:id="rId488" xr:uid="{5770871D-2F96-490F-9745-4B4976E5E989}"/>
+    <hyperlink ref="D490" r:id="rId489" xr:uid="{BA2808AA-1970-49D0-AB31-4B9DD7971A6B}"/>
+    <hyperlink ref="D491" r:id="rId490" xr:uid="{AE4247E4-0448-4CD3-9718-785AA9D4A835}"/>
+    <hyperlink ref="D492" r:id="rId491" xr:uid="{DBB7279F-805B-404E-A4F4-43F2A346CECB}"/>
+    <hyperlink ref="D493" r:id="rId492" xr:uid="{561618B7-3336-4DB7-B9E0-E63F0BE2012D}"/>
+    <hyperlink ref="D494" r:id="rId493" xr:uid="{18044B4E-CCFB-4C6D-A5FE-8DFBAE41C2FB}"/>
+    <hyperlink ref="D495" r:id="rId494" xr:uid="{CB662E9B-F3E7-4008-9958-614606B1DE77}"/>
+    <hyperlink ref="D496" r:id="rId495" xr:uid="{04C608C0-131B-44F2-8693-8277BC9E5870}"/>
+    <hyperlink ref="D497" r:id="rId496" xr:uid="{299191D2-CA2F-4A71-98A5-B86D7EE6DFDA}"/>
+    <hyperlink ref="D498" r:id="rId497" xr:uid="{60258071-58C4-467F-A157-FE40BF5FB36F}"/>
+    <hyperlink ref="D499" r:id="rId498" xr:uid="{1934ECAE-5EAD-47BF-86A3-1C2EAC300E29}"/>
+    <hyperlink ref="D500" r:id="rId499" xr:uid="{14EA8170-C163-46D3-B42B-511B85BCEC2A}"/>
+    <hyperlink ref="D501" r:id="rId500" xr:uid="{FE579644-11F4-479E-ABD7-A0CC8D3D0258}"/>
+    <hyperlink ref="D502" r:id="rId501" xr:uid="{331761AA-B6A8-429B-8F4E-641C4288515F}"/>
+    <hyperlink ref="D503" r:id="rId502" xr:uid="{52824EB2-A9BF-4676-9FE8-A608BD0EE12F}"/>
+    <hyperlink ref="D504" r:id="rId503" xr:uid="{A9B5F6F4-3280-4760-AB2B-0000B52E79EB}"/>
+    <hyperlink ref="D505" r:id="rId504" xr:uid="{743E8D52-CCB5-4213-A5E7-64B93380083B}"/>
+    <hyperlink ref="D506" r:id="rId505" xr:uid="{941BD666-293F-4F87-9FA0-5048BA055E5C}"/>
+    <hyperlink ref="D507" r:id="rId506" xr:uid="{077B4C6B-4ED3-4824-AF0D-074C0F700A34}"/>
+    <hyperlink ref="D508" r:id="rId507" xr:uid="{F7BD2A2C-272A-4B0A-B347-1D7922AFB39D}"/>
+    <hyperlink ref="D509" r:id="rId508" xr:uid="{04E3E791-C2F7-479E-8EC5-570483967BB3}"/>
+    <hyperlink ref="D510" r:id="rId509" xr:uid="{007496CA-13FD-4CCF-9BC9-4EDEE794856B}"/>
+    <hyperlink ref="D511" r:id="rId510" xr:uid="{0744B565-F453-4A78-9FB7-86A212E65318}"/>
+    <hyperlink ref="D512" r:id="rId511" xr:uid="{F6A20DFE-DF15-4379-844F-9F92083C03DA}"/>
+    <hyperlink ref="D513" r:id="rId512" xr:uid="{3FD23B17-86B2-4F49-9395-8CDD5BB7A843}"/>
+    <hyperlink ref="D514" r:id="rId513" xr:uid="{A532357F-D371-483E-86CF-A5326FF497A5}"/>
+    <hyperlink ref="D515" r:id="rId514" xr:uid="{67E497FF-C0B2-48DC-8E2D-2B74FD98EC21}"/>
+    <hyperlink ref="D516" r:id="rId515" xr:uid="{0BFE4F8D-BE17-476A-8214-D7FB716CF930}"/>
+    <hyperlink ref="D517" r:id="rId516" xr:uid="{76F4313C-69AA-4D7A-AE3A-8D8A0D75ED80}"/>
+    <hyperlink ref="D518" r:id="rId517" xr:uid="{1D40CE8D-2748-4B3C-8FB5-2CAE686BA5A5}"/>
+    <hyperlink ref="D519" r:id="rId518" xr:uid="{8433D3BB-8B04-4DBF-BF19-1C7257A49A1C}"/>
+    <hyperlink ref="D520" r:id="rId519" xr:uid="{A2D02164-6BE0-4D95-A281-CE6E4169014C}"/>
+    <hyperlink ref="D521" r:id="rId520" xr:uid="{DBC97ADA-4C5D-4D1C-AA6E-2DA022D0825B}"/>
+    <hyperlink ref="D522" r:id="rId521" xr:uid="{9975AA88-6269-498C-A661-1FB6F18361C4}"/>
+    <hyperlink ref="D523" r:id="rId522" xr:uid="{B2658CC2-5E29-4D8E-925C-B2DCBB79D01A}"/>
+    <hyperlink ref="D524" r:id="rId523" xr:uid="{BA714895-F8A2-4BA8-924D-A628DF4DED23}"/>
+    <hyperlink ref="D525" r:id="rId524" xr:uid="{4959D138-B435-400F-AA40-6E7B60C2EE48}"/>
+    <hyperlink ref="D526" r:id="rId525" xr:uid="{A32F6F4B-4F10-48D2-A25A-AEA2A077E40F}"/>
+    <hyperlink ref="D527" r:id="rId526" xr:uid="{C0A8C04F-2FD5-41A9-AC29-63B9FDA1289C}"/>
+    <hyperlink ref="D528" r:id="rId527" xr:uid="{B698E7C2-A494-4672-94E7-ECD535FCDD0D}"/>
+    <hyperlink ref="D529" r:id="rId528" xr:uid="{0B4E7938-AB7D-4DCE-81ED-B81FB73AD5E9}"/>
+    <hyperlink ref="D530" r:id="rId529" xr:uid="{6BFA15B6-6BF7-41D4-984C-5C95EE5257D2}"/>
+    <hyperlink ref="D531" r:id="rId530" xr:uid="{9E1CEF27-7E95-4AB1-A343-A391BFF33D93}"/>
+    <hyperlink ref="D532" r:id="rId531" xr:uid="{D476AA0F-341B-4F37-A28C-0430CE419382}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\00- EELU\Advising Data\advisor-finder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF2FC8D-5598-4769-9687-AF01A2D87137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7813636A-16E8-4D6E-A4C4-0DEC99EB8C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1815" windowWidth="29040" windowHeight="15720" xr2:uid="{1912A759-5108-4608-88A6-33A8F4C2828A}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="704">
   <si>
     <t>Student ID</t>
   </si>
@@ -1689,6 +1689,471 @@
   </si>
   <si>
     <t>tihababdelaziz@eelu.edu.eg</t>
+  </si>
+  <si>
+    <t>دينا عادل عيسى ابراهيم</t>
+  </si>
+  <si>
+    <t>رؤى ياسر صوفى محمود</t>
+  </si>
+  <si>
+    <t>رامي نصر همام معوض</t>
+  </si>
+  <si>
+    <t>رجب ناصر يونس صديق</t>
+  </si>
+  <si>
+    <t>رحمة رمضان عبدالله عبدالسميع</t>
+  </si>
+  <si>
+    <t>رحمة محمد السيد مصطفي</t>
+  </si>
+  <si>
+    <t>رحمة محمد طه احمد</t>
+  </si>
+  <si>
+    <t>رمضان إسماعيل مصطفى علي</t>
+  </si>
+  <si>
+    <t>رنا سيد ابو عميره صابر</t>
+  </si>
+  <si>
+    <t>رهف محمد عمر احمد</t>
+  </si>
+  <si>
+    <t>روان احمد علي عبدالمطلب</t>
+  </si>
+  <si>
+    <t>روان علوانى عبدالوهاب على</t>
+  </si>
+  <si>
+    <t>روان يحي عبدالسميع عبدالحميد معبد</t>
+  </si>
+  <si>
+    <t>روضة جمعة السيد احمد</t>
+  </si>
+  <si>
+    <t>ريم ابراهيم عبدالحي محمد</t>
+  </si>
+  <si>
+    <t>ريم ايمن احمد محمد مصطفى</t>
+  </si>
+  <si>
+    <t>ريم ايهاب كمال سيد</t>
+  </si>
+  <si>
+    <t>ريم راضى السيد عيد</t>
+  </si>
+  <si>
+    <t>ريم محمود علي علي</t>
+  </si>
+  <si>
+    <t>ريم نبيل انور عبدالحكيم</t>
+  </si>
+  <si>
+    <t>ريهام عبدالتواب محمد عبدالفتاح</t>
+  </si>
+  <si>
+    <t>زايد ابراهيم سليمان عياد</t>
+  </si>
+  <si>
+    <t>زهوه احمد محمود حافظ</t>
+  </si>
+  <si>
+    <t>زياد احمد عبدالسميع عبدالحميد</t>
+  </si>
+  <si>
+    <t>زياد سيد محمد حسن</t>
+  </si>
+  <si>
+    <t>زياد عاطف عبدالعظيم محمود</t>
+  </si>
+  <si>
+    <t>زياد نور الدين عبدالتواب محمد علي</t>
+  </si>
+  <si>
+    <t>زينب أحمد مصطفى فؤاد</t>
+  </si>
+  <si>
+    <t>زينب علي السيد علي</t>
+  </si>
+  <si>
+    <t>سارة أحمد محمود فرغلي</t>
+  </si>
+  <si>
+    <t>سارة احمد صلاح الدين خالد</t>
+  </si>
+  <si>
+    <t>سارة محمد مصطفى عيد</t>
+  </si>
+  <si>
+    <t>ساره احمد محمد احمد سيد</t>
+  </si>
+  <si>
+    <t>ساره اكرم سيد عثمان</t>
+  </si>
+  <si>
+    <t>ساره محمود احمد رمضان</t>
+  </si>
+  <si>
+    <t>ساندى فرحات حنا سليمان</t>
+  </si>
+  <si>
+    <t>ساندي نعيم وهيب جرجس</t>
+  </si>
+  <si>
+    <t>سلسبيل محمد عبدالرحمن رمضان</t>
+  </si>
+  <si>
+    <t>سلسبيل مصطفى ابراهيم توفيق أحمد مؤمن</t>
+  </si>
+  <si>
+    <t>سلمى احمد ابراهيم علواني</t>
+  </si>
+  <si>
+    <t>سلمى طارق فرغل عبدالعظيم</t>
+  </si>
+  <si>
+    <t>سلمى عادل محمود أحمد</t>
+  </si>
+  <si>
+    <t>سلمى عبد الجواد محمد عبدالله</t>
+  </si>
+  <si>
+    <t>سلمى محمد علي محمد</t>
+  </si>
+  <si>
+    <t>سلمي جمال شعبان عبداللطيف</t>
+  </si>
+  <si>
+    <t>سما احمد سعيد زكي</t>
+  </si>
+  <si>
+    <t>سما رمضان يونس عبد الحفيظ</t>
+  </si>
+  <si>
+    <t>سما هانى عبدالعظيم عطيه</t>
+  </si>
+  <si>
+    <t>سهيله محمد صدقي امين</t>
+  </si>
+  <si>
+    <t>سيد شعبان سيد فوزي</t>
+  </si>
+  <si>
+    <t>سيف الدين محمود ميلاد عبد المحسن</t>
+  </si>
+  <si>
+    <t>سيف الله كمال الدين فاوي سيد</t>
+  </si>
+  <si>
+    <t>شاهنده خلف حنفى محمود جوده</t>
+  </si>
+  <si>
+    <t>شذى محمد عباس محمد خليفه</t>
+  </si>
+  <si>
+    <t>شروق معوض عبدالحميد عبدالمولي</t>
+  </si>
+  <si>
+    <t>شريف اشرف أحمد امين</t>
+  </si>
+  <si>
+    <t>عبدالرحمن عويس رمضان السيد علي</t>
+  </si>
+  <si>
+    <t>عبدالعزيز رجب عبدالعزيز عباس</t>
+  </si>
+  <si>
+    <t>على محمد على عبدالسلام</t>
+  </si>
+  <si>
+    <t>على يحيى احمد فتح الله</t>
+  </si>
+  <si>
+    <t>علي الدين عصام إسماعيل عبد التواب علي</t>
+  </si>
+  <si>
+    <t>علي حسني حسن تمام</t>
+  </si>
+  <si>
+    <t>علي صلاح علي فرج الله حسن علي الشريف</t>
+  </si>
+  <si>
+    <t>علي محمد علي حسن</t>
+  </si>
+  <si>
+    <t>علي ياسر عمار محمد عبدالجواد</t>
+  </si>
+  <si>
+    <t>علياء عاطف عبدالتواب عبدالوهاب</t>
+  </si>
+  <si>
+    <t>عماد رجب عبدالهادي محمود</t>
+  </si>
+  <si>
+    <t>عمار احمد عيد عبدالباقي</t>
+  </si>
+  <si>
+    <t>عمار محمود جمعه على سيد</t>
+  </si>
+  <si>
+    <t>عمر أحمد رمضان محمد</t>
+  </si>
+  <si>
+    <t>عمر اشرف عبد الفتاح عبد الفضيل</t>
+  </si>
+  <si>
+    <t>عمر سامح رحيم عبدالعال</t>
+  </si>
+  <si>
+    <t>عمر عبدالرحمن عبدالستار عبدالعزيز</t>
+  </si>
+  <si>
+    <t>عمر عماد محمد عبدالخالق</t>
+  </si>
+  <si>
+    <t>عمر محمد ابراهيم عبدالسلام</t>
+  </si>
+  <si>
+    <t>عمر محمد سيد علي أبو العينين</t>
+  </si>
+  <si>
+    <t>عمر محمد سيد محمد توفيق</t>
+  </si>
+  <si>
+    <t>عمر ناصر يوسف سيد</t>
+  </si>
+  <si>
+    <t>عمر هاشم رمضان هاشم</t>
+  </si>
+  <si>
+    <t>عمرو احمد عبدالسلام عبدالمجيد</t>
+  </si>
+  <si>
+    <t>كريم خالد محمد عبدالباقى</t>
+  </si>
+  <si>
+    <t>منه أحمد محمد عبد العظيم</t>
+  </si>
+  <si>
+    <t>منه الله احمد محمد عبد التواب</t>
+  </si>
+  <si>
+    <t>منه الله عاشور قنديل محمد</t>
+  </si>
+  <si>
+    <t>م. بسمة باسم</t>
+  </si>
+  <si>
+    <t>bmashraqi@eelu.edu.eg</t>
+  </si>
+  <si>
+    <t>أحمد خالد محمد خالد</t>
+  </si>
+  <si>
+    <t>ابراهيم محمود ابراهيم غنيم</t>
+  </si>
+  <si>
+    <t>احمد اسحق احمد معوض</t>
+  </si>
+  <si>
+    <t>احمد عصام نبيل احمد احمد جاد</t>
+  </si>
+  <si>
+    <t>احمد عمر جمعه احمد عبدالرحيم</t>
+  </si>
+  <si>
+    <t>احمد فوزي على محمود</t>
+  </si>
+  <si>
+    <t>شاهندا محمد ربيع محمد</t>
+  </si>
+  <si>
+    <t>ضحى فتحى شعبان عبد الله</t>
+  </si>
+  <si>
+    <t>طارق خالد محمد محمد</t>
+  </si>
+  <si>
+    <t>طارق يونس حمدى يونس</t>
+  </si>
+  <si>
+    <t>عبد الرحمن محمد محمد خضر</t>
+  </si>
+  <si>
+    <t>عبد الرحمن وليد مرزوق محمود</t>
+  </si>
+  <si>
+    <t>عبد الله حسين صلاح أحمد</t>
+  </si>
+  <si>
+    <t>عبدالحميد سامى عبدالحميد محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن احمد حسونه شعبان حسن</t>
+  </si>
+  <si>
+    <t>عبدالرحمن جمعه على سعيد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد محمود عبدالحميد</t>
+  </si>
+  <si>
+    <t>عبدالعزيز محمد عبدالعزيز عبدالباقي</t>
+  </si>
+  <si>
+    <t>عزة حسان حلمي ابراهيم على</t>
+  </si>
+  <si>
+    <t>علياء علي حسن محمود</t>
+  </si>
+  <si>
+    <t>علياء عويس فتحي عبدالهادي</t>
+  </si>
+  <si>
+    <t>عمر أحمد عبد القادر عبد السلام</t>
+  </si>
+  <si>
+    <t>عمر محمد عبدالرحمن عبدالخالق</t>
+  </si>
+  <si>
+    <t>عمر ياسر محمد على</t>
+  </si>
+  <si>
+    <t>عمرو خالد مرسى محمد</t>
+  </si>
+  <si>
+    <t>مريم ابراهيم محمد مرسى حسن</t>
+  </si>
+  <si>
+    <t>مريم ربيع رمضان عبدالسميع</t>
+  </si>
+  <si>
+    <t>ملك عبدالهادى عبدالكريم عبدالغنى</t>
+  </si>
+  <si>
+    <t>ملك محمد احمد هلال سليمان</t>
+  </si>
+  <si>
+    <t>ملك محمد سيد احمد</t>
+  </si>
+  <si>
+    <t>منار نصر ابراهيم جنيدي</t>
+  </si>
+  <si>
+    <t>منة الله محمد الهامي عبد الباقي</t>
+  </si>
+  <si>
+    <t>منه الله رمضان محمد فتحى سيد</t>
+  </si>
+  <si>
+    <t>منه الله سيد مبروك حسن جمعه</t>
+  </si>
+  <si>
+    <t>منه الله ياسر يحيى محمود سعداوي</t>
+  </si>
+  <si>
+    <t>مهند احمد فرج الله صميدة</t>
+  </si>
+  <si>
+    <t>مى عبدالهادي عبدالكريم عبدالغني</t>
+  </si>
+  <si>
+    <t>مينا طارق صادق ملوكه</t>
+  </si>
+  <si>
+    <t>نورهان محسن فاضل محمود</t>
+  </si>
+  <si>
+    <t>نورهان محمد كمال عبدالحفيظ</t>
+  </si>
+  <si>
+    <t>نورهان ياسر حسين عبدالواحد</t>
+  </si>
+  <si>
+    <t>هاجر ايهاب ابراهيم عبد النبى</t>
+  </si>
+  <si>
+    <t>هاجر محمد سيد معوض</t>
+  </si>
+  <si>
+    <t>هاشم خالد هاشم عثمان</t>
+  </si>
+  <si>
+    <t>هالة ماهر محمد عبدالسلام</t>
+  </si>
+  <si>
+    <t>هبه الله عامر محمد سلومه</t>
+  </si>
+  <si>
+    <t>هدى حسن احمد محمود</t>
+  </si>
+  <si>
+    <t>هشام اسامه ادريس محمد</t>
+  </si>
+  <si>
+    <t>هنا حمزه اسماعيل على ابراهيم</t>
+  </si>
+  <si>
+    <t>هنا محمد احمد زكريا</t>
+  </si>
+  <si>
+    <t>هنا ياسر محمد ابراهيم</t>
+  </si>
+  <si>
+    <t>هند سيد محمود محمد</t>
+  </si>
+  <si>
+    <t>وسام خالد فتحي عيد محمود عيد</t>
+  </si>
+  <si>
+    <t>ياسمين سيد خليفة رجب اسماعيل</t>
+  </si>
+  <si>
+    <t>ياسمين عشرى جابر على</t>
+  </si>
+  <si>
+    <t>ياسمين محسن يوسف محمد</t>
+  </si>
+  <si>
+    <t>ياسمين محمد عنانى احمد ابو القاسم</t>
+  </si>
+  <si>
+    <t>يمنى ابوالخير احمد محمد</t>
+  </si>
+  <si>
+    <t>يمنى حسام عبدالستار سعيد</t>
+  </si>
+  <si>
+    <t>يمنى عمادالدين وضاح حافظ</t>
+  </si>
+  <si>
+    <t>يمني كمال عبد الهادي موسي</t>
+  </si>
+  <si>
+    <t>يمني محمد قرني محمد عبدالجواد</t>
+  </si>
+  <si>
+    <t>يوحنا عماد يوسف توفيق معوض</t>
+  </si>
+  <si>
+    <t>يوسف احمد السيد محمد</t>
+  </si>
+  <si>
+    <t>يوسف سامح شعبان رمضان</t>
+  </si>
+  <si>
+    <t>يوسف سعد حليم مسعود</t>
+  </si>
+  <si>
+    <t>يوسف محمد عبد المنعم لطفي</t>
+  </si>
+  <si>
+    <t>د. هديــر علي</t>
+  </si>
+  <si>
+    <t>hshabib@eelu.edu.eg</t>
   </si>
 </sst>
 </file>
@@ -2076,7 +2541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507AC9FC-3305-4A8E-963E-423E46E70006}">
-  <dimension ref="A1:D532"/>
+  <dimension ref="A1:D683"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
@@ -9531,6 +9996,2120 @@
       </c>
       <c r="D532" s="2" t="s">
         <v>548</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A533" s="1">
+        <v>2400435</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C533" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D533" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A534" s="1">
+        <v>2401387</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C534" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D534" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A535" s="1">
+        <v>2300320</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C535" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D535" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A536" s="1">
+        <v>2303015</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C536" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D536" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A537" s="1">
+        <v>2202014</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C537" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D537" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A538" s="1">
+        <v>2301871</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C538" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D538" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A539" s="1">
+        <v>2400364</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C539" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D539" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A540" s="1">
+        <v>2400005</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D540" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A541" s="1">
+        <v>2400408</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C541" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D541" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A542" s="1">
+        <v>2400443</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D542" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A543" s="1">
+        <v>2401039</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D543" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A544" s="1">
+        <v>2402133</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C544" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D544" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A545" s="1">
+        <v>2202018</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C545" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D545" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A546" s="1">
+        <v>2200714</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D546" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A547" s="1">
+        <v>2400580</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C547" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D547" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A548" s="1">
+        <v>2201975</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C548" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D548" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A549" s="1">
+        <v>2400367</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C549" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D549" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A550" s="1">
+        <v>2400536</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C550" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D550" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A551" s="1">
+        <v>2400111</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C551" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D551" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A552" s="1">
+        <v>2401620</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C552" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D552" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A553" s="1">
+        <v>2202008</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C553" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D553" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A554" s="1">
+        <v>2302537</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C554" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D554" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A555" s="1">
+        <v>2400519</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C555" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D555" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A556" s="1">
+        <v>2401040</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C556" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D556" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A557" s="1">
+        <v>2400842</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C557" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D557" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A558" s="1">
+        <v>2400492</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C558" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D558" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A559" s="1">
+        <v>2400733</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C559" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D559" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A560" s="1">
+        <v>2400160</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C560" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D560" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A561" s="1">
+        <v>2300301</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C561" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D561" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A562" s="1">
+        <v>2400354</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C562" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D562" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A563" s="1">
+        <v>2400505</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C563" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D563" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A564" s="1">
+        <v>2401628</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C564" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D564" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A565" s="1">
+        <v>2400379</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C565" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D565" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A566" s="1">
+        <v>2400493</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C566" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D566" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A567" s="1">
+        <v>2200803</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C567" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D567" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A568" s="1">
+        <v>2400401</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C568" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D568" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A569" s="1">
+        <v>2400439</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C569" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D569" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A570" s="1">
+        <v>2300089</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C570" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D570" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A571" s="1">
+        <v>2400386</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C571" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D571" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A572" s="1">
+        <v>2401633</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="C572" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D572" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A573" s="1">
+        <v>2400403</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D573" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A574" s="1">
+        <v>2400407</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C574" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D574" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A575" s="1">
+        <v>2400740</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D575" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A576" s="1">
+        <v>2300324</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C576" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D576" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A577" s="1">
+        <v>2400357</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C577" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D577" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A578" s="1">
+        <v>2400433</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C578" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D578" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A579" s="1">
+        <v>2402134</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C579" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D579" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A580" s="1">
+        <v>2401610</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C580" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D580" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A581" s="1">
+        <v>2302228</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C581" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D581" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A582" s="1">
+        <v>2302020</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C582" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D582" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A583" s="1">
+        <v>2303119</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C583" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D583" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A584" s="1">
+        <v>2400249</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C584" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D584" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A585" s="1">
+        <v>2302100</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D585" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A586" s="1">
+        <v>2400585</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D586" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A587" s="1">
+        <v>2401384</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C587" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D587" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A588" s="1">
+        <v>2300312</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D588" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A589" s="1">
+        <v>2500143</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D589" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A590" s="1">
+        <v>2301130</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C590" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D590" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A591" s="1">
+        <v>2503647</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C591" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D591" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A592" s="1">
+        <v>2302030</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C592" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D592" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A593" s="1">
+        <v>2501907</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="C593" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D593" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A594" s="1">
+        <v>2501565</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C594" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D594" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A595" s="1">
+        <v>2500199</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D595" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A596" s="1">
+        <v>2501423</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C596" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D596" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A597" s="1">
+        <v>2303570</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C597" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D597" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A598" s="1">
+        <v>2500498</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C598" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D598" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A599" s="1">
+        <v>2500016</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="C599" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D599" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A600" s="1">
+        <v>2501424</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C600" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D600" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A601" s="1">
+        <v>2501426</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="C601" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D601" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A602" s="1">
+        <v>2500509</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D602" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A603" s="1">
+        <v>2301438</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C603" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D603" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A604" s="1">
+        <v>2202041</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C604" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D604" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A605" s="1">
+        <v>2501899</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D605" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A606" s="1">
+        <v>2503766</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D606" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A607" s="1">
+        <v>2302285</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C607" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D607" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A608" s="1">
+        <v>2500514</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D608" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A609" s="1">
+        <v>2500534</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="C609" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D609" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A610" s="1">
+        <v>2502960</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D610" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A611" s="1">
+        <v>2503172</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C611" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D611" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A612" s="1">
+        <v>2500014</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C612" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D612" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A613" s="1">
+        <v>2001980</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C613" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D613" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A614" s="1">
+        <v>2401626</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C614" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D614" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A615" s="1">
+        <v>2300338</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C615" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D615" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A616" s="1">
+        <v>2300229</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D616" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A617" s="1">
+        <v>2001748</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C617" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D617" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A618" s="1">
+        <v>2200440</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C618" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D618" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A619" s="1">
+        <v>2200430</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="C619" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D619" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A620" s="1">
+        <v>2203001</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C620" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D620" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A621" s="1">
+        <v>2102446</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C621" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D621" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A622" s="1">
+        <v>2200448</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C622" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D622" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A623" s="1">
+        <v>2101622</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C623" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D623" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A624" s="1">
+        <v>2303503</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D624" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A625" s="1">
+        <v>2303345</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C625" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D625" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A626" s="1">
+        <v>2200455</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="C626" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D626" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A627" s="1">
+        <v>2303225</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="C627" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D627" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A628" s="1">
+        <v>2303521</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C628" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D628" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A629" s="1">
+        <v>2303226</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C629" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D629" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A630" s="1">
+        <v>2303621</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C630" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D630" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A631" s="1">
+        <v>2202565</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C631" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D631" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A632" s="1">
+        <v>2200491</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="C632" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D632" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A633" s="1">
+        <v>2301427</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C633" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D633" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A634" s="1">
+        <v>2302733</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D634" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A635" s="1">
+        <v>2200497</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C635" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D635" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A636" s="1">
+        <v>2302932</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="C636" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D636" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A637" s="1">
+        <v>2303342</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D637" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A638" s="1">
+        <v>2200485</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D638" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A639" s="1">
+        <v>2200559</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D639" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A640" s="1">
+        <v>2200469</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C640" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D640" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A641" s="1">
+        <v>2303260</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C641" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D641" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A642" s="1">
+        <v>2102437</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C642" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D642" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A643" s="1">
+        <v>2102325</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C643" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D643" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A644" s="1">
+        <v>2503919</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C644" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D644" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A645" s="1">
+        <v>2503342</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C645" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D645" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A646" s="1">
+        <v>2503344</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C646" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D646" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A647" s="1">
+        <v>2200503</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C647" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D647" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A648" s="1">
+        <v>2200528</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C648" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D648" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A649" s="1">
+        <v>2503722</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C649" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D649" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A650" s="1">
+        <v>2501282</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C650" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D650" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A651" s="1">
+        <v>2200429</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C651" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D651" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A652" s="1">
+        <v>2502679</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="C652" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D652" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A653" s="1">
+        <v>2503182</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="C653" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D653" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A654" s="1">
+        <v>2501292</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="C654" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D654" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A655" s="1">
+        <v>2502677</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="C655" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D655" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A656" s="1">
+        <v>2503765</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D656" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A657" s="1">
+        <v>2501289</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="C657" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D657" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A658" s="1">
+        <v>2400614</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C658" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D658" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A659" s="1">
+        <v>2401533</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="C659" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D659" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A660" s="1">
+        <v>2303483</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="C660" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D660" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A661" s="1">
+        <v>2403676</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C661" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D661" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A662" s="1">
+        <v>2503499</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C662" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D662" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A663" s="1">
+        <v>2503332</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="C663" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D663" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A664" s="1">
+        <v>2503011</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="C664" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D664" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A665" s="1">
+        <v>2503335</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="C665" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D665" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A666" s="1">
+        <v>2301490</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D666" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A667" s="1">
+        <v>2501286</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="C667" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D667" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A668" s="1">
+        <v>2301903</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="C668" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D668" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A669" s="1">
+        <v>2302763</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="C669" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D669" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A670" s="1">
+        <v>2501293</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C670" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D670" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A671" s="1">
+        <v>2303493</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D671" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A672" s="1">
+        <v>2502370</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="C672" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D672" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A673" s="1">
+        <v>2400784</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="C673" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D673" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A674" s="1">
+        <v>2402953</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C674" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D674" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A675" s="1">
+        <v>2501273</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="C675" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D675" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A676" s="1">
+        <v>2502875</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="C676" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D676" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A677" s="1">
+        <v>2503848</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C677" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D677" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A678" s="1">
+        <v>2501281</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="C678" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D678" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A679" s="1">
+        <v>2503945</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="C679" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D679" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A680" s="1">
+        <v>2501277</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C680" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D680" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A681" s="1">
+        <v>2401853</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C681" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D681" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A682" s="1">
+        <v>2301031</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="C682" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D682" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A683" s="1">
+        <v>2503498</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C683" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="D683" s="2" t="s">
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -10067,6 +12646,157 @@
     <hyperlink ref="D530" r:id="rId529" xr:uid="{6BFA15B6-6BF7-41D4-984C-5C95EE5257D2}"/>
     <hyperlink ref="D531" r:id="rId530" xr:uid="{9E1CEF27-7E95-4AB1-A343-A391BFF33D93}"/>
     <hyperlink ref="D532" r:id="rId531" xr:uid="{D476AA0F-341B-4F37-A28C-0430CE419382}"/>
+    <hyperlink ref="D533" r:id="rId532" xr:uid="{32FA5B5A-7AB6-477B-B07D-A5F4DBB4877B}"/>
+    <hyperlink ref="D534" r:id="rId533" xr:uid="{1D8A88F5-54DE-4B67-92A4-9D377765D557}"/>
+    <hyperlink ref="D535" r:id="rId534" xr:uid="{555DD5F7-473C-4B91-A293-DF05FDABE478}"/>
+    <hyperlink ref="D536" r:id="rId535" xr:uid="{914F4921-BA01-43E9-B478-E2AB0BBB83BF}"/>
+    <hyperlink ref="D537" r:id="rId536" xr:uid="{4101F9EE-6778-43C6-A277-CCCB4F18F71D}"/>
+    <hyperlink ref="D538" r:id="rId537" xr:uid="{97164D0C-C847-495C-A994-F0DD60F50520}"/>
+    <hyperlink ref="D539" r:id="rId538" xr:uid="{A9E9EADA-394F-4A01-8649-98E39AF811DE}"/>
+    <hyperlink ref="D540" r:id="rId539" xr:uid="{E9E3B2A2-F220-45FE-9FD7-14E20AA310AF}"/>
+    <hyperlink ref="D541" r:id="rId540" xr:uid="{53894AA9-9777-435D-BBDD-48F5BDCC8AFB}"/>
+    <hyperlink ref="D542" r:id="rId541" xr:uid="{5C9AC13A-D5B2-4685-89B8-BA78B93C8BBA}"/>
+    <hyperlink ref="D543" r:id="rId542" xr:uid="{5E5CDA7E-7BC5-4552-9E19-9D2AB280A53B}"/>
+    <hyperlink ref="D544" r:id="rId543" xr:uid="{AF2EF5D8-CE2F-419C-83C5-124101CC23D0}"/>
+    <hyperlink ref="D545" r:id="rId544" xr:uid="{135D6456-427C-414B-A30B-A331E2EAE82D}"/>
+    <hyperlink ref="D546" r:id="rId545" xr:uid="{625F1820-C8E3-44D4-A44B-ADF904BBB4FF}"/>
+    <hyperlink ref="D547" r:id="rId546" xr:uid="{0947EA82-105E-48D3-A90E-F7976990547F}"/>
+    <hyperlink ref="D548" r:id="rId547" xr:uid="{B5ED8720-94F7-42CE-9E2C-530D22090165}"/>
+    <hyperlink ref="D549" r:id="rId548" xr:uid="{DA9B2610-4AA2-464F-90C5-3AF23B56BD28}"/>
+    <hyperlink ref="D550" r:id="rId549" xr:uid="{5802C03A-B9D6-49BC-A0F0-C34EEFF833A8}"/>
+    <hyperlink ref="D551" r:id="rId550" xr:uid="{979F38E7-DB8E-49E5-AE21-4581BA385FD6}"/>
+    <hyperlink ref="D552" r:id="rId551" xr:uid="{1498195C-0F50-4517-B17F-5A3758938DE1}"/>
+    <hyperlink ref="D553" r:id="rId552" xr:uid="{80C4F9E4-E6FB-4C86-BCFE-58240CE78875}"/>
+    <hyperlink ref="D554" r:id="rId553" xr:uid="{545ACAE9-E93F-4E6A-A7F8-2F3B0E651DCD}"/>
+    <hyperlink ref="D555" r:id="rId554" xr:uid="{3D1A0CA7-5F27-4319-B231-5ADC232060DA}"/>
+    <hyperlink ref="D556" r:id="rId555" xr:uid="{8B4915D2-D1D1-4134-8C2B-41688D8BD9CB}"/>
+    <hyperlink ref="D557" r:id="rId556" xr:uid="{BED6C180-2FD6-466A-8FA1-D1E254BC8D8B}"/>
+    <hyperlink ref="D558" r:id="rId557" xr:uid="{C7D1DAA5-E426-4741-9048-B85EFE1E91B6}"/>
+    <hyperlink ref="D559" r:id="rId558" xr:uid="{19BFF5B2-6719-4625-ABE9-23AC7DE1865D}"/>
+    <hyperlink ref="D560" r:id="rId559" xr:uid="{5127AB17-C0BB-459B-B422-C740142C74E6}"/>
+    <hyperlink ref="D561" r:id="rId560" xr:uid="{F466971F-F93E-4AA9-83AE-16CFF934DC9F}"/>
+    <hyperlink ref="D562" r:id="rId561" xr:uid="{293DA1FC-D4D4-4309-9B85-CB3392D72E7C}"/>
+    <hyperlink ref="D563" r:id="rId562" xr:uid="{D102CE43-8EBC-4FB6-B326-57218536F622}"/>
+    <hyperlink ref="D564" r:id="rId563" xr:uid="{CB2FA5D5-4A56-4424-AE0A-5DCC3219EF04}"/>
+    <hyperlink ref="D565" r:id="rId564" xr:uid="{19671C1F-FBD2-4B45-A345-D40E8CD20260}"/>
+    <hyperlink ref="D566" r:id="rId565" xr:uid="{1644299D-8D4E-497A-82C0-635A0D3C5284}"/>
+    <hyperlink ref="D567" r:id="rId566" xr:uid="{22FAD931-0BB6-44AA-9015-E03DA2156F6D}"/>
+    <hyperlink ref="D568" r:id="rId567" xr:uid="{A5EC54C9-FA5D-435C-90B8-63501C0352E0}"/>
+    <hyperlink ref="D569" r:id="rId568" xr:uid="{D16654F9-11D1-4796-BE42-AA4D84B4E6A1}"/>
+    <hyperlink ref="D570" r:id="rId569" xr:uid="{301AFA6D-8500-40A5-BBF5-93545D99D8A4}"/>
+    <hyperlink ref="D571" r:id="rId570" xr:uid="{5B218B0F-EB22-4C2B-9A74-FB6432434D24}"/>
+    <hyperlink ref="D572" r:id="rId571" xr:uid="{750C37ED-84EC-437E-BC41-53F26BF92872}"/>
+    <hyperlink ref="D573" r:id="rId572" xr:uid="{63A6B6AE-58BA-406C-8F2D-7C63FE890B3C}"/>
+    <hyperlink ref="D574" r:id="rId573" xr:uid="{7EA7CD34-0B80-4CB2-8EFF-F4422069D461}"/>
+    <hyperlink ref="D575" r:id="rId574" xr:uid="{01DC92A8-DDA7-436E-B2F3-671F8D16E101}"/>
+    <hyperlink ref="D576" r:id="rId575" xr:uid="{31D6FB46-8DA2-4150-BF35-E355118E6F07}"/>
+    <hyperlink ref="D577" r:id="rId576" xr:uid="{3E5B1A7D-E14D-4781-8F98-E820C42A388C}"/>
+    <hyperlink ref="D578" r:id="rId577" xr:uid="{6D7AB84E-CCCB-4674-8D65-F4122419D81A}"/>
+    <hyperlink ref="D579" r:id="rId578" xr:uid="{8699F2A2-853D-4128-A2F5-DEAC61F5BB1F}"/>
+    <hyperlink ref="D580" r:id="rId579" xr:uid="{76E0AB4E-8489-415F-9B4B-C6F0F56978E0}"/>
+    <hyperlink ref="D581" r:id="rId580" xr:uid="{744EA59D-E909-4341-8646-E6BBD2EB7442}"/>
+    <hyperlink ref="D582" r:id="rId581" xr:uid="{8A12AB8D-82BF-4827-B8F3-DBA53C9C180A}"/>
+    <hyperlink ref="D583" r:id="rId582" xr:uid="{AE3C7642-9489-425E-B7D6-0636228C5FDA}"/>
+    <hyperlink ref="D584" r:id="rId583" xr:uid="{B3E3F707-2488-419F-B383-2743D7D098A1}"/>
+    <hyperlink ref="D585" r:id="rId584" xr:uid="{AE36A503-721F-4B5A-B6D8-20D7DCBB50F3}"/>
+    <hyperlink ref="D586" r:id="rId585" xr:uid="{DB65DFAA-1F30-4076-83BC-9083836FE8F8}"/>
+    <hyperlink ref="D587" r:id="rId586" xr:uid="{79221FA6-5394-4C36-8E09-C17D091AFAA1}"/>
+    <hyperlink ref="D588" r:id="rId587" xr:uid="{182BA53A-924B-461D-993F-624D62E4A299}"/>
+    <hyperlink ref="D589" r:id="rId588" xr:uid="{917412D6-A355-484E-99A8-191B1B58CC59}"/>
+    <hyperlink ref="D590" r:id="rId589" xr:uid="{A093DE82-61B4-47EC-9265-81F6E43B0A30}"/>
+    <hyperlink ref="D591" r:id="rId590" xr:uid="{93156088-5045-499E-AC33-B84ACC320126}"/>
+    <hyperlink ref="D592" r:id="rId591" xr:uid="{892033C0-F126-41F3-9EEF-7145447CAD34}"/>
+    <hyperlink ref="D593" r:id="rId592" xr:uid="{CD4F431B-0102-432F-B35C-60681151B7D9}"/>
+    <hyperlink ref="D594" r:id="rId593" xr:uid="{E864CB55-0EAA-48D5-9427-2EBD2DE87C58}"/>
+    <hyperlink ref="D595" r:id="rId594" xr:uid="{2E1A45A5-6813-4FCD-8C11-33D0F6A364FD}"/>
+    <hyperlink ref="D596" r:id="rId595" xr:uid="{ADA97ED8-6BB8-499E-8785-41C4EE50208D}"/>
+    <hyperlink ref="D597" r:id="rId596" xr:uid="{F57BB7E6-949A-4C10-AD76-4CA21BB9E05B}"/>
+    <hyperlink ref="D598" r:id="rId597" xr:uid="{AA532E47-5FF4-4A0C-A65C-FE1587C22EAF}"/>
+    <hyperlink ref="D599" r:id="rId598" xr:uid="{8C52FDC3-CD67-4F91-B656-3F8FE231E6FD}"/>
+    <hyperlink ref="D600" r:id="rId599" xr:uid="{2B6581CC-F696-4CB9-9678-CDE47DB25BB9}"/>
+    <hyperlink ref="D601" r:id="rId600" xr:uid="{829DA4C1-EB44-4F6C-888B-299331D3B761}"/>
+    <hyperlink ref="D602" r:id="rId601" xr:uid="{972E40B2-6100-4416-9EBC-0024C35B7FD9}"/>
+    <hyperlink ref="D603" r:id="rId602" xr:uid="{DB01D011-CD0A-4328-952B-7DF183C470A9}"/>
+    <hyperlink ref="D604" r:id="rId603" xr:uid="{C50785C2-80FE-4F0D-9A6F-ED1A8EC37074}"/>
+    <hyperlink ref="D605" r:id="rId604" xr:uid="{BB04492F-6B1C-4507-AB3F-7EC126BD8E4E}"/>
+    <hyperlink ref="D606" r:id="rId605" xr:uid="{A802451B-7E13-464D-BE37-4054B2755F68}"/>
+    <hyperlink ref="D607" r:id="rId606" xr:uid="{D0ADD34D-EDFE-46B0-BAC3-67EAB088ADC3}"/>
+    <hyperlink ref="D608" r:id="rId607" xr:uid="{292C43FC-486D-4F90-99B8-246E13A9E74F}"/>
+    <hyperlink ref="D609" r:id="rId608" xr:uid="{6371729B-1C8D-4F01-9C32-91E736E1C62A}"/>
+    <hyperlink ref="D610" r:id="rId609" xr:uid="{054A02D4-E65F-4D28-8CF8-B2FF88FDB51B}"/>
+    <hyperlink ref="D611" r:id="rId610" xr:uid="{6C31FAD6-6A1A-4F90-8B5F-A91FFE97BF21}"/>
+    <hyperlink ref="D612" r:id="rId611" xr:uid="{38E019D3-0DBB-43FC-A519-9A5E5C99D47E}"/>
+    <hyperlink ref="D613" r:id="rId612" xr:uid="{C788DADB-6710-4444-8D84-A3650CCBE411}"/>
+    <hyperlink ref="D614" r:id="rId613" xr:uid="{32D7C23B-B0E0-49A7-B11E-0AED0ED1AE7B}"/>
+    <hyperlink ref="D615" r:id="rId614" xr:uid="{7BC0CF12-4CB4-42BC-B85C-7E65F49CADE2}"/>
+    <hyperlink ref="D616" r:id="rId615" xr:uid="{F0765AD8-7370-4E6E-BE02-359326818555}"/>
+    <hyperlink ref="D617" r:id="rId616" xr:uid="{9F582A3E-0432-4306-BF7E-28D6EE66A791}"/>
+    <hyperlink ref="D618" r:id="rId617" xr:uid="{52EDB4D8-6B71-4B5D-BB68-86F077BFE886}"/>
+    <hyperlink ref="D619" r:id="rId618" xr:uid="{89337A50-18EA-494D-943B-17D9E1C609D3}"/>
+    <hyperlink ref="D620" r:id="rId619" xr:uid="{5EEE5159-ACA0-43BF-B70C-0C8B9EEE53BE}"/>
+    <hyperlink ref="D621" r:id="rId620" xr:uid="{55793B4F-2D0D-4316-9E5F-F0B4C101D4F4}"/>
+    <hyperlink ref="D622" r:id="rId621" xr:uid="{79A2FB35-EA64-4B6F-B062-98D047595514}"/>
+    <hyperlink ref="D623" r:id="rId622" xr:uid="{8DB55BF5-9035-410C-AF05-9961C0B73000}"/>
+    <hyperlink ref="D624" r:id="rId623" xr:uid="{063D7253-082A-4A39-BF8C-D9C0E2B4B016}"/>
+    <hyperlink ref="D625" r:id="rId624" xr:uid="{E67C7794-275C-4FB0-B0B4-9F0D01EB107F}"/>
+    <hyperlink ref="D626" r:id="rId625" xr:uid="{9C89E0E0-10E9-4022-B20F-8938BFE6F640}"/>
+    <hyperlink ref="D627" r:id="rId626" xr:uid="{6ECD74DA-ED5E-4C05-AC0E-1CB4DD736F12}"/>
+    <hyperlink ref="D628" r:id="rId627" xr:uid="{E8C206F4-B8D6-440F-9FC4-34499ABC6C5B}"/>
+    <hyperlink ref="D629" r:id="rId628" xr:uid="{C79D00CE-5982-422C-A96E-F2906E30246B}"/>
+    <hyperlink ref="D630" r:id="rId629" xr:uid="{2A0E9D84-CF19-4786-945F-3FB70B757AB5}"/>
+    <hyperlink ref="D631" r:id="rId630" xr:uid="{96EA4736-CC27-4A50-80EC-49BB501530AC}"/>
+    <hyperlink ref="D632" r:id="rId631" xr:uid="{3113798B-8225-4615-BB01-7DF9DEA8DEDE}"/>
+    <hyperlink ref="D633" r:id="rId632" xr:uid="{5E3A5B12-12B5-4B4D-B989-E03E4DB28788}"/>
+    <hyperlink ref="D634" r:id="rId633" xr:uid="{C4CDB716-AB01-466D-B802-EBFC6C7F1794}"/>
+    <hyperlink ref="D635" r:id="rId634" xr:uid="{0B4A3636-09F9-49F0-A19F-A72CFEF12332}"/>
+    <hyperlink ref="D636" r:id="rId635" xr:uid="{9939B31A-E1E8-4F4F-89C9-491DE4F1B73E}"/>
+    <hyperlink ref="D637" r:id="rId636" xr:uid="{E2002972-42C9-4548-95C1-9EEE845EC957}"/>
+    <hyperlink ref="D638" r:id="rId637" xr:uid="{F1EC8DC5-1FBB-4766-B47D-87FD12661A22}"/>
+    <hyperlink ref="D639" r:id="rId638" xr:uid="{A92BEA58-136B-49EA-B8C0-FD08693B0BFD}"/>
+    <hyperlink ref="D640" r:id="rId639" xr:uid="{415C9BD4-1D51-4EE3-AF50-39E605417892}"/>
+    <hyperlink ref="D641" r:id="rId640" xr:uid="{1331DA92-DFE4-4188-9BDB-3BEC86963FC2}"/>
+    <hyperlink ref="D642" r:id="rId641" xr:uid="{32B61604-DB35-4D09-9E37-595089CCAA28}"/>
+    <hyperlink ref="D643" r:id="rId642" xr:uid="{BE86FC79-7418-450F-A171-F038D4321978}"/>
+    <hyperlink ref="D644" r:id="rId643" xr:uid="{EB073172-E0A3-4E30-B365-87129B5E7559}"/>
+    <hyperlink ref="D645" r:id="rId644" xr:uid="{5B452630-FE06-46E6-AAA7-78196E39EA68}"/>
+    <hyperlink ref="D646" r:id="rId645" xr:uid="{DAE46813-A3D8-4ECC-8E94-FC9996E0986B}"/>
+    <hyperlink ref="D647" r:id="rId646" xr:uid="{06909E9E-86D4-4225-9DE0-E4E055B13977}"/>
+    <hyperlink ref="D648" r:id="rId647" xr:uid="{75C7BC07-E393-4D5B-9084-71254C190D1C}"/>
+    <hyperlink ref="D649" r:id="rId648" xr:uid="{FE35DC98-A9A7-4E2B-AA1A-F3139585EA03}"/>
+    <hyperlink ref="D650" r:id="rId649" xr:uid="{2D6229DF-EC02-477C-B5CD-F73B8A6A8F8F}"/>
+    <hyperlink ref="D651" r:id="rId650" xr:uid="{20062277-8F7B-49F2-B72E-D2B083E6D502}"/>
+    <hyperlink ref="D652" r:id="rId651" xr:uid="{9735EF10-3279-4D17-8180-22D13090C657}"/>
+    <hyperlink ref="D653" r:id="rId652" xr:uid="{90324292-0DCC-44EF-8689-4AEDC9E4B2C2}"/>
+    <hyperlink ref="D654" r:id="rId653" xr:uid="{1A420D16-4325-4D17-A862-59FDB46F0103}"/>
+    <hyperlink ref="D655" r:id="rId654" xr:uid="{88447350-CE8B-4CDA-A01C-66C6FB340464}"/>
+    <hyperlink ref="D656" r:id="rId655" xr:uid="{6CF3B203-468C-4D7E-B2E4-CF1374796E80}"/>
+    <hyperlink ref="D657" r:id="rId656" xr:uid="{C0B789B7-7DD4-4A79-A4EC-4CC27D0AA51C}"/>
+    <hyperlink ref="D658" r:id="rId657" xr:uid="{33952340-CE58-4B01-8C27-35EF46681274}"/>
+    <hyperlink ref="D659" r:id="rId658" xr:uid="{48F80858-E2EC-4C85-9091-F7ECDABC717A}"/>
+    <hyperlink ref="D660" r:id="rId659" xr:uid="{D47CB925-2A05-436D-B85F-3AE9C6A8A183}"/>
+    <hyperlink ref="D661" r:id="rId660" xr:uid="{98DD4FA0-33C1-41F3-9090-BF69D37E8E98}"/>
+    <hyperlink ref="D662" r:id="rId661" xr:uid="{E406B39B-4133-462A-B5E4-861537901D16}"/>
+    <hyperlink ref="D663" r:id="rId662" xr:uid="{51171787-423F-4E57-A955-AEE4E6EB5397}"/>
+    <hyperlink ref="D664" r:id="rId663" xr:uid="{EDEAC009-E33A-4CF5-8D21-0C3206B991EF}"/>
+    <hyperlink ref="D665" r:id="rId664" xr:uid="{837F26C2-7133-442F-9605-5479F917B48F}"/>
+    <hyperlink ref="D666" r:id="rId665" xr:uid="{EBBF7C59-863D-4647-88E6-1A48B3475DD3}"/>
+    <hyperlink ref="D667" r:id="rId666" xr:uid="{80E30E8A-FE5B-4AE3-B9DA-C44A167006D6}"/>
+    <hyperlink ref="D668" r:id="rId667" xr:uid="{3C9D0B62-3B5F-4AA7-B093-A6D24E6ED403}"/>
+    <hyperlink ref="D669" r:id="rId668" xr:uid="{EC4B8574-FC25-4ACC-84EE-C7BE7ED47F61}"/>
+    <hyperlink ref="D670" r:id="rId669" xr:uid="{1C7143AE-18FF-4ADE-BD7B-8380960BA6E3}"/>
+    <hyperlink ref="D671" r:id="rId670" xr:uid="{73146A50-013A-407D-94F7-DADC09C9C718}"/>
+    <hyperlink ref="D672" r:id="rId671" xr:uid="{11BB1842-7F9D-479E-B6AC-C1B549219119}"/>
+    <hyperlink ref="D673" r:id="rId672" xr:uid="{A8736846-417F-4223-8A85-BFF1053404AF}"/>
+    <hyperlink ref="D674" r:id="rId673" xr:uid="{91771238-C97F-4740-990B-261BFD437D76}"/>
+    <hyperlink ref="D675" r:id="rId674" xr:uid="{EBB9037D-4517-492C-90AA-69BCE2597272}"/>
+    <hyperlink ref="D676" r:id="rId675" xr:uid="{765BB357-30A1-40F4-B482-11804A317730}"/>
+    <hyperlink ref="D677" r:id="rId676" xr:uid="{EEBA3CFA-DDC3-4A3F-A0AD-FF44710E99A2}"/>
+    <hyperlink ref="D678" r:id="rId677" xr:uid="{DDC8E745-4905-4D52-81E6-CB61C53B748B}"/>
+    <hyperlink ref="D679" r:id="rId678" xr:uid="{177818F3-77F5-49E5-B808-87904099B396}"/>
+    <hyperlink ref="D680" r:id="rId679" xr:uid="{CA30C629-25F1-4BA0-9652-0FA22893DBEA}"/>
+    <hyperlink ref="D681" r:id="rId680" xr:uid="{7532A1A0-C158-4901-BAF9-4B00E8840B26}"/>
+    <hyperlink ref="D682" r:id="rId681" xr:uid="{ABBDCE3B-A4CA-4F85-A2A6-C8B9F4B3627B}"/>
+    <hyperlink ref="D683" r:id="rId682" xr:uid="{C0ED68FA-A5A1-47F2-A8A4-FC1E3BE13CC3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\00- EELU\Advising Data\advisor-finder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42125F2E-492C-436C-AA7E-06C2C2E3916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1139573B-D5B3-46D6-8F57-737D12CAADBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1815" windowWidth="29040" windowHeight="15720" xr2:uid="{1912A759-5108-4608-88A6-33A8F4C2828A}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="1040">
   <si>
     <t>Student ID</t>
   </si>
@@ -2931,13 +2931,244 @@
   </si>
   <si>
     <t>fseoudi@eelu.edu.eg</t>
+  </si>
+  <si>
+    <t>أحمد رمضان خميس رزق</t>
+  </si>
+  <si>
+    <t>أحمد رمضان يونس امام</t>
+  </si>
+  <si>
+    <t>أحمد شعبان على محمد قطب</t>
+  </si>
+  <si>
+    <t>أروى اشرف محمد سيد</t>
+  </si>
+  <si>
+    <t>أسلام احمد فتحي احمد موسي</t>
+  </si>
+  <si>
+    <t>ايه عبدالمنعم شحاته عبدالعليم</t>
+  </si>
+  <si>
+    <t>رغد احمد حسن محمد</t>
+  </si>
+  <si>
+    <t>فاروق محمد فاروق محمد</t>
+  </si>
+  <si>
+    <t>محمد اشرف قرني محمد</t>
+  </si>
+  <si>
+    <t>محمد السيد الروبي نادي</t>
+  </si>
+  <si>
+    <t>محمد ايمن محمد عبدالوهاب</t>
+  </si>
+  <si>
+    <t>محمد ايهاب محمد كامل</t>
+  </si>
+  <si>
+    <t>محمد بدرالدين احمد حسين</t>
+  </si>
+  <si>
+    <t>محمد جمال محمد جلال</t>
+  </si>
+  <si>
+    <t>محمد حمدي امام صديق</t>
+  </si>
+  <si>
+    <t>محمد درباله عبدالحميد عبدالفتاح</t>
+  </si>
+  <si>
+    <t>محمد شعبان محمد سيد</t>
+  </si>
+  <si>
+    <t>محمد عادل ابراهيم عبد الحميد</t>
+  </si>
+  <si>
+    <t>محمد عادل محمد محمود</t>
+  </si>
+  <si>
+    <t>محمد على محمد حسانين محمد</t>
+  </si>
+  <si>
+    <t>محمد عوض مهدي ديهوم</t>
+  </si>
+  <si>
+    <t>محمد قطب هاشم عثمان</t>
+  </si>
+  <si>
+    <t>محمد محمود محمد حامد هيكل</t>
+  </si>
+  <si>
+    <t>محمد مصطفى صلاح صابر</t>
+  </si>
+  <si>
+    <t>محمود احمد محمد عبدالرازق</t>
+  </si>
+  <si>
+    <t>محمود شادي محمود عبدالمنجي</t>
+  </si>
+  <si>
+    <t>مرام احمد علي محمد</t>
+  </si>
+  <si>
+    <t>مرام اسامة فاروق مكاوي</t>
+  </si>
+  <si>
+    <t>مروان محمد سامى أحمد</t>
+  </si>
+  <si>
+    <t>مريم السيد أحمد محمد</t>
+  </si>
+  <si>
+    <t>مريم زاهر عيد رمزى</t>
+  </si>
+  <si>
+    <t>مريم محمد حسين أحمد</t>
+  </si>
+  <si>
+    <t>مريم محمد حمدي محمد</t>
+  </si>
+  <si>
+    <t>مريم محمد قرني محمد محمد</t>
+  </si>
+  <si>
+    <t>مريم محمود محمد حامد هيكل</t>
+  </si>
+  <si>
+    <t>مريم محمود محمد عبدالرحمن محمد</t>
+  </si>
+  <si>
+    <t>مريم وائل محمد مرسى</t>
+  </si>
+  <si>
+    <t>مريهان ميخائيل حنس شاكر</t>
+  </si>
+  <si>
+    <t>مصطفي محمد مصطفي محمد</t>
+  </si>
+  <si>
+    <t>ملك محمد احمد احمد</t>
+  </si>
+  <si>
+    <t>منة الله طارق مصطفى محمد حسن</t>
+  </si>
+  <si>
+    <t>منة الله محمد عبد الحميد عبد العزيز</t>
+  </si>
+  <si>
+    <t>منه الله اشرف عباس احمد فرج</t>
+  </si>
+  <si>
+    <t>منه الله ايمن احمد السيد</t>
+  </si>
+  <si>
+    <t>منه الله جمعه السايح رشوان سرحان</t>
+  </si>
+  <si>
+    <t>منه الله ياسر سيد ابو المجد</t>
+  </si>
+  <si>
+    <t>منه خالد محمد احمد</t>
+  </si>
+  <si>
+    <t>منه مصطفى محمود محمد</t>
+  </si>
+  <si>
+    <t>مهاب ايمن احمد الصغير</t>
+  </si>
+  <si>
+    <t>مي محمد كامل سيد</t>
+  </si>
+  <si>
+    <t>ميار السيد محمد مصطفى</t>
+  </si>
+  <si>
+    <t>ميرا مدحت موريس رياض</t>
+  </si>
+  <si>
+    <t>ميرا هانى فكرى حبيب توما</t>
+  </si>
+  <si>
+    <t>ميرنا عاطف رياض زكي</t>
+  </si>
+  <si>
+    <t>مينا هاني باسليوس عبدالله</t>
+  </si>
+  <si>
+    <t>ناهد علي حسين كامل</t>
+  </si>
+  <si>
+    <t>ندى محمد صلاح الدين سيد</t>
+  </si>
+  <si>
+    <t>ندى محمود أحمد محمود</t>
+  </si>
+  <si>
+    <t>نديم احمد حميدة عطوه</t>
+  </si>
+  <si>
+    <t>نرمين علي أحمد عبد الجواد</t>
+  </si>
+  <si>
+    <t>نضال عصام نبيل أحمد</t>
+  </si>
+  <si>
+    <t>نغم ابراهيم محمد يوسف</t>
+  </si>
+  <si>
+    <t>نهاد أحمد سعيد محمد السيد</t>
+  </si>
+  <si>
+    <t>نهلة احمد محمود عبداللطيف</t>
+  </si>
+  <si>
+    <t>نور الدين محمد حسين صالح</t>
+  </si>
+  <si>
+    <t>نور محمد عبدالمنعم عبدالعزيز</t>
+  </si>
+  <si>
+    <t>نور وليد محمد مصطفى</t>
+  </si>
+  <si>
+    <t>نورهان عبدالحميد محمد عبدالحميد</t>
+  </si>
+  <si>
+    <t>نورهان محمد محمود عبد التواب</t>
+  </si>
+  <si>
+    <t>نيجار وائل محمد محمود</t>
+  </si>
+  <si>
+    <t>هاجر احمد السيد عبدالله</t>
+  </si>
+  <si>
+    <t>هاجر امين محمد عبدالباقي</t>
+  </si>
+  <si>
+    <t>هاجر مصطفى على عبد الله السواح</t>
+  </si>
+  <si>
+    <t>هبه الله خالد سيد معوض قطب</t>
+  </si>
+  <si>
+    <t>yabdeltawab@eelu.edu.eg</t>
+  </si>
+  <si>
+    <t>د. يــــارا عبــد التواب</t>
+  </si>
+  <si>
+    <t>يوستينا عماد غطاس فهيم</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2953,13 +3184,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFEF9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2975,13 +3219,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3318,7 +3565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507AC9FC-3305-4A8E-963E-423E46E70006}">
-  <dimension ref="A1:D936"/>
+  <dimension ref="A1:D1011"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
@@ -16429,6 +16676,1056 @@
       </c>
       <c r="D936" s="2" t="s">
         <v>962</v>
+      </c>
+    </row>
+    <row r="937" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A937" s="1">
+        <v>2200459</v>
+      </c>
+      <c r="B937" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="C937" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D937" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="938" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A938" s="1">
+        <v>2200462</v>
+      </c>
+      <c r="B938" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="C938" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D938" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="939" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A939" s="1">
+        <v>2200454</v>
+      </c>
+      <c r="B939" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="C939" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D939" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="940" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A940" s="1">
+        <v>2202574</v>
+      </c>
+      <c r="B940" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="C940" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D940" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="941" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A941" s="1">
+        <v>2202562</v>
+      </c>
+      <c r="B941" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="C941" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D941" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="942" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A942" s="1">
+        <v>2200510</v>
+      </c>
+      <c r="B942" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="C942" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D942" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="943" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A943" s="1">
+        <v>2200519</v>
+      </c>
+      <c r="B943" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="C943" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D943" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="944" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A944" s="1">
+        <v>2200563</v>
+      </c>
+      <c r="B944" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="C944" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D944" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="945" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A945" s="1">
+        <v>2401459</v>
+      </c>
+      <c r="B945" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="C945" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D945" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="946" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A946" s="1">
+        <v>2402274</v>
+      </c>
+      <c r="B946" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="C946" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D946" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="947" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A947" s="1">
+        <v>2200477</v>
+      </c>
+      <c r="B947" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="C947" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D947" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="948" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A948" s="1">
+        <v>2403243</v>
+      </c>
+      <c r="B948" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="C948" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D948" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="949" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A949" s="1">
+        <v>2301188</v>
+      </c>
+      <c r="B949" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="C949" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D949" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="950" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A950" s="1">
+        <v>2301739</v>
+      </c>
+      <c r="B950" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="C950" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D950" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="951" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A951" s="1">
+        <v>2400602</v>
+      </c>
+      <c r="B951" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="C951" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D951" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="952" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A952" s="1">
+        <v>2202563</v>
+      </c>
+      <c r="B952" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="C952" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D952" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="953" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A953" s="1">
+        <v>2200489</v>
+      </c>
+      <c r="B953" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="C953" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D953" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="954" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A954" s="1">
+        <v>2303347</v>
+      </c>
+      <c r="B954" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="C954" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D954" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="955" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A955" s="1">
+        <v>2402700</v>
+      </c>
+      <c r="B955" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="C955" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D955" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="956" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A956" s="1">
+        <v>2302737</v>
+      </c>
+      <c r="B956" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="C956" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D956" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="957" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A957" s="1">
+        <v>2403203</v>
+      </c>
+      <c r="B957" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="C957" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D957" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="958" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A958" s="1">
+        <v>2303405</v>
+      </c>
+      <c r="B958" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="C958" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D958" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="959" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A959" s="1">
+        <v>2300698</v>
+      </c>
+      <c r="B959" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="C959" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D959" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="960" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A960" s="1">
+        <v>2402866</v>
+      </c>
+      <c r="B960" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="C960" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D960" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="961" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A961" s="1">
+        <v>2302749</v>
+      </c>
+      <c r="B961" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C961" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D961" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="962" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A962" s="1">
+        <v>2400318</v>
+      </c>
+      <c r="B962" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="C962" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D962" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="963" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A963" s="1">
+        <v>2302732</v>
+      </c>
+      <c r="B963" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="C963" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D963" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="964" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A964" s="1">
+        <v>2401743</v>
+      </c>
+      <c r="B964" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="C964" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D964" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="965" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A965" s="1">
+        <v>2400263</v>
+      </c>
+      <c r="B965" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="C965" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D965" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="966" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A966" s="1">
+        <v>2401908</v>
+      </c>
+      <c r="B966" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="C966" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D966" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="967" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A967" s="1">
+        <v>2403110</v>
+      </c>
+      <c r="B967" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="C967" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D967" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="968" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A968" s="1">
+        <v>2303481</v>
+      </c>
+      <c r="B968" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="C968" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D968" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="969" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A969" s="1">
+        <v>2403674</v>
+      </c>
+      <c r="B969" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="C969" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D969" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="970" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A970" s="1">
+        <v>2303619</v>
+      </c>
+      <c r="B970" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="C970" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D970" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="971" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A971" s="1">
+        <v>2400605</v>
+      </c>
+      <c r="B971" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="C971" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D971" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="972" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A972" s="1">
+        <v>2400607</v>
+      </c>
+      <c r="B972" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="C972" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D972" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="973" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A973" s="1">
+        <v>2301075</v>
+      </c>
+      <c r="B973" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="C973" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D973" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="974" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A974" s="1">
+        <v>2303258</v>
+      </c>
+      <c r="B974" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C974" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D974" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="975" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A975" s="1">
+        <v>2402419</v>
+      </c>
+      <c r="B975" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C975" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D975" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="976" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A976" s="1">
+        <v>2403500</v>
+      </c>
+      <c r="B976" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C976" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D976" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A977" s="1">
+        <v>2301902</v>
+      </c>
+      <c r="B977" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C977" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D977" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A978" s="1">
+        <v>2303363</v>
+      </c>
+      <c r="B978" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C978" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D978" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A979" s="1">
+        <v>2403679</v>
+      </c>
+      <c r="B979" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C979" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D979" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A980" s="1">
+        <v>2403686</v>
+      </c>
+      <c r="B980" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C980" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D980" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A981" s="1">
+        <v>2402954</v>
+      </c>
+      <c r="B981" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C981" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D981" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A982" s="1">
+        <v>2303088</v>
+      </c>
+      <c r="B982" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C982" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D982" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A983" s="1">
+        <v>2400787</v>
+      </c>
+      <c r="B983" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C983" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D983" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="984" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A984" s="1">
+        <v>2401537</v>
+      </c>
+      <c r="B984" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C984" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D984" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="985" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A985" s="1">
+        <v>2303250</v>
+      </c>
+      <c r="B985" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C985" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D985" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A986" s="1">
+        <v>2403677</v>
+      </c>
+      <c r="B986" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C986" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D986" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="987" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A987" s="1">
+        <v>2301547</v>
+      </c>
+      <c r="B987" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C987" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D987" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A988" s="1">
+        <v>2400595</v>
+      </c>
+      <c r="B988" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C988" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D988" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A989" s="1">
+        <v>2402957</v>
+      </c>
+      <c r="B989" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C989" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D989" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="990" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A990" s="1">
+        <v>2400610</v>
+      </c>
+      <c r="B990" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C990" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D990" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A991" s="1">
+        <v>2400783</v>
+      </c>
+      <c r="B991" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C991" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D991" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A992" s="1">
+        <v>2401782</v>
+      </c>
+      <c r="B992" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C992" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D992" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="993" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A993" s="1">
+        <v>2400135</v>
+      </c>
+      <c r="B993" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C993" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D993" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="994" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A994" s="1">
+        <v>2403685</v>
+      </c>
+      <c r="B994" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C994" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D994" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="995" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A995" s="1">
+        <v>2403687</v>
+      </c>
+      <c r="B995" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C995" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D995" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="996" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A996" s="1">
+        <v>2400596</v>
+      </c>
+      <c r="B996" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C996" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D996" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="997" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A997" s="1">
+        <v>2303622</v>
+      </c>
+      <c r="B997" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C997" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D997" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="998" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A998" s="1">
+        <v>2301430</v>
+      </c>
+      <c r="B998" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C998" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D998" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="999" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A999" s="1">
+        <v>2303438</v>
+      </c>
+      <c r="B999" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C999" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D999" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1000" s="1">
+        <v>2400606</v>
+      </c>
+      <c r="B1000" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C1000" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1000" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1001" s="1">
+        <v>2301940</v>
+      </c>
+      <c r="B1001" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C1001" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1001" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1002" s="1">
+        <v>2200513</v>
+      </c>
+      <c r="B1002" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C1002" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1002" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1003" s="1">
+        <v>2300699</v>
+      </c>
+      <c r="B1003" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C1003" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1003" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1004" s="1">
+        <v>2400164</v>
+      </c>
+      <c r="B1004" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C1004" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1004" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1005" s="1">
+        <v>2202568</v>
+      </c>
+      <c r="B1005" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C1005" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1005" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1006" s="1">
+        <v>2402299</v>
+      </c>
+      <c r="B1006" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C1006" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1006" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1007" s="1">
+        <v>2403722</v>
+      </c>
+      <c r="B1007" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C1007" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1007" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1008" s="1">
+        <v>2300028</v>
+      </c>
+      <c r="B1008" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C1008" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1008" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1009" s="1">
+        <v>2200495</v>
+      </c>
+      <c r="B1009" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1009" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1009" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1010" s="1">
+        <v>2203002</v>
+      </c>
+      <c r="B1010" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C1010" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1010" s="2" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1011" s="1">
+        <v>2200505</v>
+      </c>
+      <c r="B1011" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C1011" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1011" s="2" t="s">
+        <v>1037</v>
       </c>
     </row>
   </sheetData>
@@ -17369,6 +18666,81 @@
     <hyperlink ref="D934" r:id="rId933" xr:uid="{0E1023FA-5EE0-4D05-A84B-D57FCD170F6F}"/>
     <hyperlink ref="D935" r:id="rId934" xr:uid="{943E5994-949F-43FE-92B7-958A9E1434A5}"/>
     <hyperlink ref="D936" r:id="rId935" xr:uid="{6BF24128-3224-4973-B439-99D063AD943E}"/>
+    <hyperlink ref="D937" r:id="rId936" xr:uid="{DB3DAD75-493D-41E0-AE67-86D44440D8AD}"/>
+    <hyperlink ref="D938" r:id="rId937" xr:uid="{29BE314D-7095-4986-A7E5-32E75E8F1E48}"/>
+    <hyperlink ref="D939" r:id="rId938" xr:uid="{008BBE83-4632-4C64-ACD2-93E578D79DAF}"/>
+    <hyperlink ref="D940" r:id="rId939" xr:uid="{F2226B68-AA09-40E2-A29C-D952CA824863}"/>
+    <hyperlink ref="D941" r:id="rId940" xr:uid="{28242426-47A9-43B1-9743-B3D44F870C90}"/>
+    <hyperlink ref="D942" r:id="rId941" xr:uid="{1C6595E6-DBA5-49B7-9834-0D2A0FE67A90}"/>
+    <hyperlink ref="D943" r:id="rId942" xr:uid="{26D34DBD-A1EF-4D12-BDB1-C0EDA04B6E6E}"/>
+    <hyperlink ref="D944" r:id="rId943" xr:uid="{A1724BC7-36DA-4E07-811F-9C761FF81BA0}"/>
+    <hyperlink ref="D945" r:id="rId944" xr:uid="{017212F4-9027-4A7B-9274-8AEA59365894}"/>
+    <hyperlink ref="D946" r:id="rId945" xr:uid="{BBA0F45A-91C1-424F-A86F-F88FD4FB3EA3}"/>
+    <hyperlink ref="D947" r:id="rId946" xr:uid="{8C24902E-7678-4C2E-8AC9-8A61E575DE88}"/>
+    <hyperlink ref="D948" r:id="rId947" xr:uid="{EF2D67FF-E219-464F-8641-4B04CAE34B56}"/>
+    <hyperlink ref="D949" r:id="rId948" xr:uid="{448512FB-C7C4-4947-936D-1DC504F260F6}"/>
+    <hyperlink ref="D950" r:id="rId949" xr:uid="{9E7A4846-0DE6-4F3B-ACFC-F5CFF117088F}"/>
+    <hyperlink ref="D951" r:id="rId950" xr:uid="{CEF0A835-7A16-438E-B896-FE1471B81D19}"/>
+    <hyperlink ref="D952" r:id="rId951" xr:uid="{F1279B50-2457-4EF9-A3D2-FEBB60143884}"/>
+    <hyperlink ref="D953" r:id="rId952" xr:uid="{6E5BA975-3360-4750-8B61-484024CF1D1B}"/>
+    <hyperlink ref="D954" r:id="rId953" xr:uid="{9719B817-8712-4E5C-A5CB-439243A91B3C}"/>
+    <hyperlink ref="D955" r:id="rId954" xr:uid="{CCF46EE1-9EE0-4F35-9AF4-6B535FF2F8C4}"/>
+    <hyperlink ref="D956" r:id="rId955" xr:uid="{901BA55E-BE28-407F-9BC7-BC37DA3B8F17}"/>
+    <hyperlink ref="D957" r:id="rId956" xr:uid="{29DBE6FC-AC62-4AA2-9FEE-0560C0EB7891}"/>
+    <hyperlink ref="D958" r:id="rId957" xr:uid="{CD236334-F0CD-494B-9E64-53A4A217DB93}"/>
+    <hyperlink ref="D959" r:id="rId958" xr:uid="{C6C9A40C-5A34-4FA1-8EBA-D7DF79E84277}"/>
+    <hyperlink ref="D960" r:id="rId959" xr:uid="{17D35FFA-9A13-4BA7-B08E-F9729467F365}"/>
+    <hyperlink ref="D961" r:id="rId960" xr:uid="{36B3E3AB-5F1B-4551-A19E-FCB7BDA82F1F}"/>
+    <hyperlink ref="D962" r:id="rId961" xr:uid="{0357721B-A534-41A7-8A8A-1A2CF97B6C93}"/>
+    <hyperlink ref="D963" r:id="rId962" xr:uid="{3CEB749A-23CD-4BEC-B979-6EE678DC7A3C}"/>
+    <hyperlink ref="D964" r:id="rId963" xr:uid="{D4A4E4A1-0D0D-41E4-8D2E-0F5987EC9E8D}"/>
+    <hyperlink ref="D965" r:id="rId964" xr:uid="{BC80C788-25A5-4DB1-90E5-9488DBD97CCD}"/>
+    <hyperlink ref="D966" r:id="rId965" xr:uid="{E7FBFFFF-CE74-4FF1-BD66-E13F9FF45208}"/>
+    <hyperlink ref="D967" r:id="rId966" xr:uid="{A28D7EFE-5A01-4036-8E86-53215A732792}"/>
+    <hyperlink ref="D968" r:id="rId967" xr:uid="{0EE004A8-15CF-420C-94C5-FA190A582194}"/>
+    <hyperlink ref="D969" r:id="rId968" xr:uid="{16B2C049-A358-469F-BE96-9CF905928A17}"/>
+    <hyperlink ref="D970" r:id="rId969" xr:uid="{381BED87-83E7-4AA9-915A-C5807528EDA3}"/>
+    <hyperlink ref="D971" r:id="rId970" xr:uid="{BA0493D1-0361-4E8F-B853-5F5A4B0C554C}"/>
+    <hyperlink ref="D972" r:id="rId971" xr:uid="{61A0CFA5-FBFA-4839-8404-737E9932031B}"/>
+    <hyperlink ref="D973" r:id="rId972" xr:uid="{9A87F9BA-2BD2-43FC-A9FF-B552C38F4675}"/>
+    <hyperlink ref="D974" r:id="rId973" xr:uid="{8539C80E-D610-444B-83D4-FF6336E0B5E3}"/>
+    <hyperlink ref="D975" r:id="rId974" xr:uid="{811746EA-F856-47EE-9C3B-5FD06ACD1B67}"/>
+    <hyperlink ref="D976" r:id="rId975" xr:uid="{05B22C54-C3D0-4517-8F75-A304AB70B884}"/>
+    <hyperlink ref="D977" r:id="rId976" xr:uid="{84AE2DEC-A741-4EEA-85E4-C7D6A2C523B6}"/>
+    <hyperlink ref="D978" r:id="rId977" xr:uid="{378A0D0D-9E2F-4D05-9B02-CE4D918DF437}"/>
+    <hyperlink ref="D979" r:id="rId978" xr:uid="{1D3008E9-607B-4529-AFAD-967C0CF74872}"/>
+    <hyperlink ref="D980" r:id="rId979" xr:uid="{4A56B2CA-F531-4AC1-A430-E0BDCC23A184}"/>
+    <hyperlink ref="D981" r:id="rId980" xr:uid="{6B189AAA-9450-4FE8-9538-B392FDC8B0D4}"/>
+    <hyperlink ref="D982" r:id="rId981" xr:uid="{A51F6179-57D4-4480-80CE-EF8B3B58743E}"/>
+    <hyperlink ref="D983" r:id="rId982" xr:uid="{E5D8911D-1A45-4DB5-91EA-C3745F0925E6}"/>
+    <hyperlink ref="D984" r:id="rId983" xr:uid="{5F2094F3-D940-4B18-87EE-EC38B052B4FF}"/>
+    <hyperlink ref="D985" r:id="rId984" xr:uid="{677E7F66-1AD6-4B36-9930-8EEE5192D76F}"/>
+    <hyperlink ref="D986" r:id="rId985" xr:uid="{0AAA0B0C-EE30-4557-AD1D-4B20D4C63FC6}"/>
+    <hyperlink ref="D987" r:id="rId986" xr:uid="{42D13D7D-5173-40F8-8EF6-56A5D4488E51}"/>
+    <hyperlink ref="D988" r:id="rId987" xr:uid="{4532461B-9542-4315-97B1-AFF172B69FEC}"/>
+    <hyperlink ref="D989" r:id="rId988" xr:uid="{BEEEA3EF-2C1D-45EC-AB59-CB40819EFD50}"/>
+    <hyperlink ref="D990" r:id="rId989" xr:uid="{C187BBA3-998E-4631-A229-52CE59D835F4}"/>
+    <hyperlink ref="D991" r:id="rId990" xr:uid="{58840E56-465E-46FA-987E-80C537E99BF4}"/>
+    <hyperlink ref="D992" r:id="rId991" xr:uid="{82CD8640-5EA6-43EE-820C-1829C3DE282E}"/>
+    <hyperlink ref="D993" r:id="rId992" xr:uid="{0A529B43-803B-464F-8B89-E381B5D3DE5F}"/>
+    <hyperlink ref="D994" r:id="rId993" xr:uid="{92AD8F8F-D595-46F3-B1A4-06633377CE87}"/>
+    <hyperlink ref="D995" r:id="rId994" xr:uid="{182497A1-37FB-4069-8147-AC406C8C970F}"/>
+    <hyperlink ref="D996" r:id="rId995" xr:uid="{417FA222-C726-4ACE-801A-284604F2479A}"/>
+    <hyperlink ref="D997" r:id="rId996" xr:uid="{836E4A21-DE62-44C2-A43F-07A323DE4B9F}"/>
+    <hyperlink ref="D998" r:id="rId997" xr:uid="{648513A1-D079-45C9-9A9F-D6ACEAD059BB}"/>
+    <hyperlink ref="D999" r:id="rId998" xr:uid="{02BE963A-D844-4F84-9A38-D34564AD7BE3}"/>
+    <hyperlink ref="D1000" r:id="rId999" xr:uid="{80CB1CDB-C9FB-496A-8169-C5783B795991}"/>
+    <hyperlink ref="D1001" r:id="rId1000" xr:uid="{427A1FEF-8188-4431-BEBA-6CFE38ABC921}"/>
+    <hyperlink ref="D1002" r:id="rId1001" xr:uid="{48E0A74A-0CF7-49C5-91A0-8E85D6749427}"/>
+    <hyperlink ref="D1003" r:id="rId1002" xr:uid="{E2774762-E108-4FFF-8A9F-38008AA78722}"/>
+    <hyperlink ref="D1004" r:id="rId1003" xr:uid="{92288C6D-D240-4ACC-A540-24070C09C693}"/>
+    <hyperlink ref="D1005" r:id="rId1004" xr:uid="{9D2090A1-B08E-4432-9D54-9DEE8F5E3F47}"/>
+    <hyperlink ref="D1006" r:id="rId1005" xr:uid="{B0DA26A6-0C3F-4E52-809E-C17018993476}"/>
+    <hyperlink ref="D1007" r:id="rId1006" xr:uid="{70E0CA35-DE10-4E62-8972-6C4876B6B20A}"/>
+    <hyperlink ref="D1008" r:id="rId1007" xr:uid="{7FA96247-D362-404E-B37C-6933D61EFB6A}"/>
+    <hyperlink ref="D1009" r:id="rId1008" xr:uid="{1F4B9FEE-4E5F-4F91-99E5-3E815CC0DF5C}"/>
+    <hyperlink ref="D1010" r:id="rId1009" xr:uid="{FB91E5FE-7AD3-44D3-9427-AF197B3D8EC8}"/>
+    <hyperlink ref="D1011" r:id="rId1010" xr:uid="{A5813BEC-429B-4A9A-9C84-C1B9FBD1E32D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\00- EELU\Advising Data\advisor-finder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70281F3-76F8-4429-8E61-E9199B6A202F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6570D144-B3E3-4AD4-8AEF-3ADEDDF4193E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1912A759-5108-4608-88A6-33A8F4C2828A}"/>
+    <workbookView xWindow="7035" yWindow="1350" windowWidth="21600" windowHeight="11295" xr2:uid="{1912A759-5108-4608-88A6-33A8F4C2828A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3562" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="1314">
   <si>
     <t>Student ID</t>
   </si>
@@ -3702,6 +3702,288 @@
   </si>
   <si>
     <t>imohsenfikirin@eelu.edu.eg</t>
+  </si>
+  <si>
+    <t>أحمد شريف حسن سيد</t>
+  </si>
+  <si>
+    <t>احمد جمال احمد محمد</t>
+  </si>
+  <si>
+    <t>احمد حمدى احمد سعد</t>
+  </si>
+  <si>
+    <t>احمد ربيع احمد محمد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد سليمان</t>
+  </si>
+  <si>
+    <t>احمد محمد صلاح حسن احمد</t>
+  </si>
+  <si>
+    <t>احمد محمود ابراهيم عبدالعاطي</t>
+  </si>
+  <si>
+    <t>ادهم السيد السيد حسان</t>
+  </si>
+  <si>
+    <t>اسامة اسماعيل عبدالله اسماعيل</t>
+  </si>
+  <si>
+    <t>اسامه نادي عبد التواب محمد</t>
+  </si>
+  <si>
+    <t>اسلام احمد رشوان فرغلي رشوان</t>
+  </si>
+  <si>
+    <t>اسلام سعد عبدالتواب رجب</t>
+  </si>
+  <si>
+    <t>اسلام محمد طه محمد</t>
+  </si>
+  <si>
+    <t>اسلام محمد عبدالله عبدالعليم</t>
+  </si>
+  <si>
+    <t>الاء احمد رمضان احمد</t>
+  </si>
+  <si>
+    <t>الحسين طارق عبدالسميع علي</t>
+  </si>
+  <si>
+    <t>امنه حازم فؤاد مصطفى</t>
+  </si>
+  <si>
+    <t>امين سيد امين عبداللطيف</t>
+  </si>
+  <si>
+    <t>انس محمود سيد محمد</t>
+  </si>
+  <si>
+    <t>اياد محمد عبدالعزيز خالد</t>
+  </si>
+  <si>
+    <t>اية محمود سعيد منسي</t>
+  </si>
+  <si>
+    <t>ايمان عبدالله محمود احمد</t>
+  </si>
+  <si>
+    <t>ايمن محمد السيد اسماعيل</t>
+  </si>
+  <si>
+    <t>ايه ايهاب عبدالتواب محمود</t>
+  </si>
+  <si>
+    <t>ايه ربيع احمد محمد</t>
+  </si>
+  <si>
+    <t>ايه قرني مصطفي حسين</t>
+  </si>
+  <si>
+    <t>ايه محمد ثروت خلف</t>
+  </si>
+  <si>
+    <t>بدر محمد صالح خالد</t>
+  </si>
+  <si>
+    <t>بسملة جمال شعبان أحمد</t>
+  </si>
+  <si>
+    <t>بسملة عماد عبد السميع امين</t>
+  </si>
+  <si>
+    <t>بسمله احمد شوبك عبدالستار</t>
+  </si>
+  <si>
+    <t>بسمله حمدي ابراهيم عبدالحافظ</t>
+  </si>
+  <si>
+    <t>بسمله محمد عوض احمد</t>
+  </si>
+  <si>
+    <t>بولا ميلاد وصفى سليم</t>
+  </si>
+  <si>
+    <t>حبيبة عزت عبدالتواب سالم خليل</t>
+  </si>
+  <si>
+    <t>حسام جابر قطب على</t>
+  </si>
+  <si>
+    <t>حسين عيد فاروق على</t>
+  </si>
+  <si>
+    <t>حفصه احمد فاروق احمد</t>
+  </si>
+  <si>
+    <t>دينا محمد عاشور محمود</t>
+  </si>
+  <si>
+    <t>رنيم حجازي سيد رمضان</t>
+  </si>
+  <si>
+    <t>روان عماد مصطفى سيد</t>
+  </si>
+  <si>
+    <t>روان محمد فضل محمود</t>
+  </si>
+  <si>
+    <t>ريم طه محمد شعبان السيد</t>
+  </si>
+  <si>
+    <t>زياد محمود فتحى عبد الفتاح قاسم</t>
+  </si>
+  <si>
+    <t>ساره سامر سمير بطرس</t>
+  </si>
+  <si>
+    <t>ساره ياسر جابر صميده</t>
+  </si>
+  <si>
+    <t>سهيلة عبد الناصر محمد الشيمي</t>
+  </si>
+  <si>
+    <t>شروق جمعة محمد عبدالبصير</t>
+  </si>
+  <si>
+    <t>شهد احمد زايد عبد الحكيم حماده</t>
+  </si>
+  <si>
+    <t>شهد محمود مصطفى محمود</t>
+  </si>
+  <si>
+    <t>شيماء صلاح محمد عبدالحميد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد احمد علي</t>
+  </si>
+  <si>
+    <t>علياء هشام اسماعيل حمزه</t>
+  </si>
+  <si>
+    <t>عمار عيد صلاح عبد الغنى</t>
+  </si>
+  <si>
+    <t>عمرو محمد علي محمد</t>
+  </si>
+  <si>
+    <t>فاطمة الزهراء محمد احمد محمد</t>
+  </si>
+  <si>
+    <t>فاطمة وليد سيد محمد</t>
+  </si>
+  <si>
+    <t>فاطمه محمد ربيع مجاهد</t>
+  </si>
+  <si>
+    <t>فرونيا ايهاب رشدى مهنى</t>
+  </si>
+  <si>
+    <t>كريم علي احمد علي</t>
+  </si>
+  <si>
+    <t>كيفن اشرف ابراهيم صليب</t>
+  </si>
+  <si>
+    <t>لقاء سامح عبدالمنعم محمد</t>
+  </si>
+  <si>
+    <t>مارفي فايز كمال لطف الله</t>
+  </si>
+  <si>
+    <t>مايكل ابراهيم معوض ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد بكر سعد على</t>
+  </si>
+  <si>
+    <t>محمد حمدى محمد شاكر</t>
+  </si>
+  <si>
+    <t>محمد رجب معوض السيد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد محمد</t>
+  </si>
+  <si>
+    <t>محمد صلاح سعيد دسوقى</t>
+  </si>
+  <si>
+    <t>محمد محمود امين حسن محمد الطيب</t>
+  </si>
+  <si>
+    <t>محمد محمود عبد المجيد كامل</t>
+  </si>
+  <si>
+    <t>محمود عبدالتواب عبدالمهدى محمد</t>
+  </si>
+  <si>
+    <t>محمود محمد عبد الجواد احمد</t>
+  </si>
+  <si>
+    <t>مرام ايمن محمد علي احمد</t>
+  </si>
+  <si>
+    <t>مريم اشرف محمد عبدالتواب</t>
+  </si>
+  <si>
+    <t>مريم ايمن عطا الله شهدي</t>
+  </si>
+  <si>
+    <t>مريم صلاح الدين محمد اسماعيل السيد</t>
+  </si>
+  <si>
+    <t>مريم مصطفى معوض عبدالمجيد</t>
+  </si>
+  <si>
+    <t>مصطفى محمود عثمان صديق</t>
+  </si>
+  <si>
+    <t>معتز عيسى أحمد عيسى</t>
+  </si>
+  <si>
+    <t>منار علي حماد جودة</t>
+  </si>
+  <si>
+    <t>منة الله مدحت محمود وصفي</t>
+  </si>
+  <si>
+    <t>منه احمد عبد الفتاح احمد</t>
+  </si>
+  <si>
+    <t>منه احمد مجدى محمد حافظ</t>
+  </si>
+  <si>
+    <t>منه عبدالناصر محمود صبره</t>
+  </si>
+  <si>
+    <t>مي احمد سيد محمد</t>
+  </si>
+  <si>
+    <t>ميراى شنودة صبحى بباوى</t>
+  </si>
+  <si>
+    <t>هاجر محمد محمود السيد</t>
+  </si>
+  <si>
+    <t>وجيه ايهاب وجيه جرجس</t>
+  </si>
+  <si>
+    <t>وسام اشرف سيد محمد</t>
+  </si>
+  <si>
+    <t>ياسمين حمدالله احمد خليل</t>
+  </si>
+  <si>
+    <t>rewais@eelu.edu.eg</t>
+  </si>
+  <si>
+    <t>م. رغـــــدة محمــــــــود</t>
   </si>
 </sst>
 </file>
@@ -4105,7 +4387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507AC9FC-3305-4A8E-963E-423E46E70006}">
-  <dimension ref="A1:D1187"/>
+  <dimension ref="A1:D1279"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -20730,6 +21012,1294 @@
       </c>
       <c r="D1187" s="1" t="s">
         <v>1219</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1188" s="1">
+        <v>2400844</v>
+      </c>
+      <c r="B1188" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C1188" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1188" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1189" s="1">
+        <v>2300287</v>
+      </c>
+      <c r="B1189" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C1189" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1189" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1190" s="1">
+        <v>2202034</v>
+      </c>
+      <c r="B1190" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1190" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1190" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1191" s="1">
+        <v>2302029</v>
+      </c>
+      <c r="B1191" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C1191" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1191" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1192" s="1">
+        <v>2302026</v>
+      </c>
+      <c r="B1192" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C1192" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1192" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1193" s="1">
+        <v>2202049</v>
+      </c>
+      <c r="B1193" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C1193" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1193" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1194" s="1">
+        <v>2300250</v>
+      </c>
+      <c r="B1194" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C1194" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1194" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1195" s="1">
+        <v>2201950</v>
+      </c>
+      <c r="B1195" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1195" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1195" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1196" s="1">
+        <v>2302222</v>
+      </c>
+      <c r="B1196" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C1196" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1196" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1197" s="1">
+        <v>2300175</v>
+      </c>
+      <c r="B1197" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C1197" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1197" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1198" s="1">
+        <v>2302083</v>
+      </c>
+      <c r="B1198" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C1198" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1198" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1199" s="1">
+        <v>2301791</v>
+      </c>
+      <c r="B1199" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C1199" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1199" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1200" s="1">
+        <v>2202039</v>
+      </c>
+      <c r="B1200" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C1200" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1200" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1201" s="1">
+        <v>2202048</v>
+      </c>
+      <c r="B1201" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C1201" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1201" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1202" s="1">
+        <v>2502209</v>
+      </c>
+      <c r="B1202" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C1202" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1202" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1203" s="1">
+        <v>2200917</v>
+      </c>
+      <c r="B1203" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C1203" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1203" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1204" s="1">
+        <v>2301164</v>
+      </c>
+      <c r="B1204" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C1204" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1204" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1205" s="1">
+        <v>2302282</v>
+      </c>
+      <c r="B1205" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C1205" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1205" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1206" s="1">
+        <v>2202026</v>
+      </c>
+      <c r="B1206" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C1206" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1206" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1207" s="1">
+        <v>2500546</v>
+      </c>
+      <c r="B1207" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C1207" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1207" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1208" s="1">
+        <v>2502277</v>
+      </c>
+      <c r="B1208" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C1208" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1208" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1209" s="1">
+        <v>2200517</v>
+      </c>
+      <c r="B1209" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C1209" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1209" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1210" s="1">
+        <v>2503246</v>
+      </c>
+      <c r="B1210" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C1210" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1210" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1211" s="1">
+        <v>2500015</v>
+      </c>
+      <c r="B1211" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C1211" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1211" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1212" s="1">
+        <v>2300247</v>
+      </c>
+      <c r="B1212" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C1212" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1212" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1213" s="1">
+        <v>2503029</v>
+      </c>
+      <c r="B1213" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C1213" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1213" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1214" s="1">
+        <v>2500198</v>
+      </c>
+      <c r="B1214" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C1214" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1214" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1215" s="1">
+        <v>2503016</v>
+      </c>
+      <c r="B1215" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C1215" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1215" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1216" s="1">
+        <v>2503808</v>
+      </c>
+      <c r="B1216" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C1216" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1216" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1217" s="1">
+        <v>2500472</v>
+      </c>
+      <c r="B1217" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C1217" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1217" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1218" s="1">
+        <v>2300264</v>
+      </c>
+      <c r="B1218" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C1218" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1218" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1219" s="1">
+        <v>2503744</v>
+      </c>
+      <c r="B1219" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C1219" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1219" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1220" s="1">
+        <v>2500486</v>
+      </c>
+      <c r="B1220" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C1220" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1220" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1221" s="1">
+        <v>2302067</v>
+      </c>
+      <c r="B1221" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C1221" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1221" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1222" s="1">
+        <v>2300290</v>
+      </c>
+      <c r="B1222" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C1222" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1222" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1223" s="1">
+        <v>2300285</v>
+      </c>
+      <c r="B1223" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C1223" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1223" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1224" s="1">
+        <v>2202051</v>
+      </c>
+      <c r="B1224" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C1224" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1224" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1225" s="1">
+        <v>2301543</v>
+      </c>
+      <c r="B1225" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1225" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1225" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1226" s="1">
+        <v>2300288</v>
+      </c>
+      <c r="B1226" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C1226" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1226" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1227" s="1">
+        <v>2300249</v>
+      </c>
+      <c r="B1227" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C1227" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1227" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1228" s="1">
+        <v>2300278</v>
+      </c>
+      <c r="B1228" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C1228" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1228" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1229" s="1">
+        <v>2302065</v>
+      </c>
+      <c r="B1229" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C1229" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1229" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1230" s="1">
+        <v>2300263</v>
+      </c>
+      <c r="B1230" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C1230" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1230" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1231" s="1">
+        <v>2302082</v>
+      </c>
+      <c r="B1231" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C1231" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1231" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1232" s="1">
+        <v>2300267</v>
+      </c>
+      <c r="B1232" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C1232" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1232" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1233" s="1">
+        <v>2300280</v>
+      </c>
+      <c r="B1233" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C1233" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1233" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1234" s="1">
+        <v>2303614</v>
+      </c>
+      <c r="B1234" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C1234" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1234" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1235" s="1">
+        <v>2300255</v>
+      </c>
+      <c r="B1235" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C1235" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1235" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1236" s="1">
+        <v>2302074</v>
+      </c>
+      <c r="B1236" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C1236" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1236" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1237" s="1">
+        <v>2302081</v>
+      </c>
+      <c r="B1237" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C1237" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1237" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1238" s="1">
+        <v>2300284</v>
+      </c>
+      <c r="B1238" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C1238" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1238" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1239" s="1">
+        <v>2300276</v>
+      </c>
+      <c r="B1239" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C1239" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1239" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1240" s="1">
+        <v>2300283</v>
+      </c>
+      <c r="B1240" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C1240" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1240" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1241" s="1">
+        <v>2302807</v>
+      </c>
+      <c r="B1241" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C1241" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1241" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1242" s="1">
+        <v>2200794</v>
+      </c>
+      <c r="B1242" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C1242" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1242" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1243" s="1">
+        <v>2300258</v>
+      </c>
+      <c r="B1243" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C1243" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1243" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1244" s="1">
+        <v>2300281</v>
+      </c>
+      <c r="B1244" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C1244" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1244" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1245" s="1">
+        <v>2300291</v>
+      </c>
+      <c r="B1245" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C1245" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1245" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1246" s="1">
+        <v>2302318</v>
+      </c>
+      <c r="B1246" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C1246" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1246" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1247" s="1">
+        <v>2200786</v>
+      </c>
+      <c r="B1247" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C1247" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1247" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1248" s="1">
+        <v>2301790</v>
+      </c>
+      <c r="B1248" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C1248" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1248" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1249" s="1">
+        <v>2302058</v>
+      </c>
+      <c r="B1249" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C1249" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1249" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1250" s="1">
+        <v>2300272</v>
+      </c>
+      <c r="B1250" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C1250" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1250" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1251" s="1">
+        <v>2300275</v>
+      </c>
+      <c r="B1251" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C1251" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1251" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1252" s="1">
+        <v>2300259</v>
+      </c>
+      <c r="B1252" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C1252" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1252" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1253" s="1">
+        <v>2302080</v>
+      </c>
+      <c r="B1253" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C1253" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1253" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1254" s="1">
+        <v>2300268</v>
+      </c>
+      <c r="B1254" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C1254" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1254" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1255" s="1">
+        <v>2202028</v>
+      </c>
+      <c r="B1255" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C1255" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1255" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1256" s="1">
+        <v>2301542</v>
+      </c>
+      <c r="B1256" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C1256" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1256" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1257" s="1">
+        <v>2202031</v>
+      </c>
+      <c r="B1257" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C1257" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1257" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1258" s="1">
+        <v>2202063</v>
+      </c>
+      <c r="B1258" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C1258" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1258" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1259" s="1">
+        <v>2302068</v>
+      </c>
+      <c r="B1259" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C1259" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1259" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1260" s="1">
+        <v>2300252</v>
+      </c>
+      <c r="B1260" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C1260" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1260" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1261" s="1">
+        <v>2301546</v>
+      </c>
+      <c r="B1261" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C1261" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1261" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1262" s="1">
+        <v>2300030</v>
+      </c>
+      <c r="B1262" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C1262" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1262" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1263" s="1">
+        <v>2301545</v>
+      </c>
+      <c r="B1263" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C1263" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1263" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1264" s="1">
+        <v>2302064</v>
+      </c>
+      <c r="B1264" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C1264" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1264" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1265" s="1">
+        <v>2302060</v>
+      </c>
+      <c r="B1265" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C1265" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1265" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1266" s="1">
+        <v>2300279</v>
+      </c>
+      <c r="B1266" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C1266" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1266" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1267" s="1">
+        <v>2300254</v>
+      </c>
+      <c r="B1267" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C1267" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1267" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1268" s="1">
+        <v>2300266</v>
+      </c>
+      <c r="B1268" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C1268" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1268" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1269" s="1">
+        <v>2302073</v>
+      </c>
+      <c r="B1269" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C1269" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1269" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1270" s="1">
+        <v>2202070</v>
+      </c>
+      <c r="B1270" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C1270" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1270" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1271" s="1">
+        <v>2300282</v>
+      </c>
+      <c r="B1271" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C1271" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1271" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1272" s="1">
+        <v>2300260</v>
+      </c>
+      <c r="B1272" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C1272" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1272" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1273" s="1">
+        <v>2500540</v>
+      </c>
+      <c r="B1273" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C1273" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1273" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1274" s="1">
+        <v>2500506</v>
+      </c>
+      <c r="B1274" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C1274" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1274" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1275" s="1">
+        <v>2302072</v>
+      </c>
+      <c r="B1275" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C1275" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1275" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1276" s="1">
+        <v>2300270</v>
+      </c>
+      <c r="B1276" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C1276" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1276" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1277" s="1">
+        <v>2300269</v>
+      </c>
+      <c r="B1277" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1277" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1277" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1278" s="1">
+        <v>2300039</v>
+      </c>
+      <c r="B1278" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C1278" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1278" s="2" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1279" s="1">
+        <v>2300277</v>
+      </c>
+      <c r="B1279" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C1279" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1279" s="2" t="s">
+        <v>1312</v>
       </c>
     </row>
   </sheetData>
@@ -21836,6 +23406,8 @@
     <hyperlink ref="D1100" r:id="rId1099" xr:uid="{409E1479-D572-4E25-85C3-7D235290BAFA}"/>
     <hyperlink ref="D1101" r:id="rId1100" xr:uid="{CB48B6C8-C29A-4914-AA72-BF68ADDCD9BD}"/>
     <hyperlink ref="D1102" r:id="rId1101" xr:uid="{14BC1FA7-CB78-415C-894A-BEB16C8D5A9A}"/>
+    <hyperlink ref="D1188" r:id="rId1102" xr:uid="{EAFD5C1A-0156-4D8E-9C11-1413314FB42D}"/>
+    <hyperlink ref="D1189:D1279" r:id="rId1103" display="rewais@eelu.edu.eg" xr:uid="{E8B709D3-B661-4C9A-A8BA-45D694772EAF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\00- EELU\Advising Data\advisor-finder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6570D144-B3E3-4AD4-8AEF-3ADEDDF4193E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AED57BA-C023-48D1-92B1-F49266C0FD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7035" yWindow="1350" windowWidth="21600" windowHeight="11295" xr2:uid="{1912A759-5108-4608-88A6-33A8F4C2828A}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="1314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4369" uniqueCount="1495">
   <si>
     <t>Student ID</t>
   </si>
@@ -3984,13 +3984,556 @@
   </si>
   <si>
     <t>م. رغـــــدة محمــــــــود</t>
+  </si>
+  <si>
+    <t>اريج هاني عزت عبدالحليم</t>
+  </si>
+  <si>
+    <t>اسامه احمد محمود عبداللطيف</t>
+  </si>
+  <si>
+    <t>اسلم محمد علي محمد بدوي</t>
+  </si>
+  <si>
+    <t>اسماء حسين عبدالحميد احمد</t>
+  </si>
+  <si>
+    <t>محمد أشرف عبد العزيز ناصف</t>
+  </si>
+  <si>
+    <t>محمد احمد حسنى قاسم</t>
+  </si>
+  <si>
+    <t>محمد احمد زيدان عويس</t>
+  </si>
+  <si>
+    <t>محمد احمد عبد الخالق على</t>
+  </si>
+  <si>
+    <t>محمد احمد محسن اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد احمد محمد عبد الله</t>
+  </si>
+  <si>
+    <t>محمد احمد محمد عبدالله سعد</t>
+  </si>
+  <si>
+    <t>محمد احمد محمود السيد عليوه</t>
+  </si>
+  <si>
+    <t>محمد احمد محمود عبدالباسط محمد</t>
+  </si>
+  <si>
+    <t>محمد اكرم عبدالسميع محمد على</t>
+  </si>
+  <si>
+    <t>محمد جمال حسن احمد</t>
+  </si>
+  <si>
+    <t>محمد رشوان علي أمين</t>
+  </si>
+  <si>
+    <t>محمد سعيد مصطفي ابراهيم علي</t>
+  </si>
+  <si>
+    <t>محمد صادق محمد صادق</t>
+  </si>
+  <si>
+    <t>محمد عاطف نورالدين رمضان</t>
+  </si>
+  <si>
+    <t>محمد عبدالله حسين موسى</t>
+  </si>
+  <si>
+    <t>محمد عمرو مصطفى يوسف</t>
+  </si>
+  <si>
+    <t>محمد عيد أحمد أمين أحمد</t>
+  </si>
+  <si>
+    <t>محمد كارم عبدالهادي محمد</t>
+  </si>
+  <si>
+    <t>منه محمد فتحي عبدالهادي</t>
+  </si>
+  <si>
+    <t>مهاب ناصر احمد على</t>
+  </si>
+  <si>
+    <t>موسي زين العابدين عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مى اشرف محمد رضا زيان</t>
+  </si>
+  <si>
+    <t>ميار سامح السيد علي متولي</t>
+  </si>
+  <si>
+    <t>ميرنا زكريا عبداللطيف ابراهيم</t>
+  </si>
+  <si>
+    <t>مينا جورج فايز فهمي</t>
+  </si>
+  <si>
+    <t>نادر سامي نثان غبريال</t>
+  </si>
+  <si>
+    <t>نادر سيد خليل حميده</t>
+  </si>
+  <si>
+    <t>نادين خالد عبدالفتاح حسن</t>
+  </si>
+  <si>
+    <t>نانسي محمود أحمد محمد</t>
+  </si>
+  <si>
+    <t>ندا عبدالعظيم عيد حجازي</t>
+  </si>
+  <si>
+    <t>ندا ممدوح كامل عويس</t>
+  </si>
+  <si>
+    <t>ندى على احمد على</t>
+  </si>
+  <si>
+    <t>ندي رمضان شعبان رزق</t>
+  </si>
+  <si>
+    <t>ندي مراد احمد عبدالتواب</t>
+  </si>
+  <si>
+    <t>نرفانه ميلاد ذكي غالي</t>
+  </si>
+  <si>
+    <t>نهال عمرو كمال علي</t>
+  </si>
+  <si>
+    <t>نور عبدالحميد محمد عبدالحميد</t>
+  </si>
+  <si>
+    <t>نور محمد عبدالرحمن عثمان</t>
+  </si>
+  <si>
+    <t>نورا احمد يوسف علي</t>
+  </si>
+  <si>
+    <t>نوران احمد فؤاد عيد</t>
+  </si>
+  <si>
+    <t>نورهان سيد يوسف محمود</t>
+  </si>
+  <si>
+    <t>هاجر عادل ابوزيد طلبه</t>
+  </si>
+  <si>
+    <t>هاجر كامل محمد كامل</t>
+  </si>
+  <si>
+    <t>هاجر محمد عبدالعظيم عبدالعليم</t>
+  </si>
+  <si>
+    <t>هاجر محمود عبد الحميد خبيري</t>
+  </si>
+  <si>
+    <t>هادى احمد سيد فتحى</t>
+  </si>
+  <si>
+    <t>هبه ابراهيم احمد عثمان</t>
+  </si>
+  <si>
+    <t>هدير عبد الناصر سيد عبدالحميد</t>
+  </si>
+  <si>
+    <t>هشام مصطفي احمد عبدالجيد</t>
+  </si>
+  <si>
+    <t>هنا ايمن احمد امين</t>
+  </si>
+  <si>
+    <t>هنا محمد احمد ابراهيم سلامه</t>
+  </si>
+  <si>
+    <t>هناء عاطف خالد محمد</t>
+  </si>
+  <si>
+    <t>وسام شعبان موسى على</t>
+  </si>
+  <si>
+    <t>ولاء سعيد عثمان رمضان</t>
+  </si>
+  <si>
+    <t>يارا عطيه فتحي علي</t>
+  </si>
+  <si>
+    <t>ياسمين ناصر شحاته احمد</t>
+  </si>
+  <si>
+    <t>ياسين محمد سيد محمود</t>
+  </si>
+  <si>
+    <t>يسرا محمد عزت حنفى</t>
+  </si>
+  <si>
+    <t>يمنى عمرو سمير عبدالرازق</t>
+  </si>
+  <si>
+    <t>يمنى محمد الأمير ربيع عبدالعزيز</t>
+  </si>
+  <si>
+    <t>يمنى ياسر مصطفى رجب</t>
+  </si>
+  <si>
+    <t>يمني عبدالعزيز عوض عبدالعزيز</t>
+  </si>
+  <si>
+    <t>يمني محمد ابراهيم عبدالحليم</t>
+  </si>
+  <si>
+    <t>يوسف أشرف فاروق أحمد جودة</t>
+  </si>
+  <si>
+    <t>يوسف اثناسيوس سمير عزيز</t>
+  </si>
+  <si>
+    <t>يوسف احمد ابراهيم رمضان</t>
+  </si>
+  <si>
+    <t>يوسف احمد رجب عبد الرحمن</t>
+  </si>
+  <si>
+    <t>يوسف اشرف حمدون صالح</t>
+  </si>
+  <si>
+    <t>يوسف بدر الدين ربيع علي السيد</t>
+  </si>
+  <si>
+    <t>يوسف بدر مكرم عياد</t>
+  </si>
+  <si>
+    <t>يوسف حسين فاروق إبراهيم</t>
+  </si>
+  <si>
+    <t>يوسف خالد علي عبدالمجيد</t>
+  </si>
+  <si>
+    <t>يوسف خميس على حمد عبدالقادر</t>
+  </si>
+  <si>
+    <t>يوسف داود اسرائيل ميلاد</t>
+  </si>
+  <si>
+    <t>يوسف ذاكر الله السيد عبد التواب عويس</t>
+  </si>
+  <si>
+    <t>يوسف سامح محمد عبدالنبي</t>
+  </si>
+  <si>
+    <t>يوسف عايد يوسف عشيري</t>
+  </si>
+  <si>
+    <t>يوسف عماد شفيق جرجس</t>
+  </si>
+  <si>
+    <t>يوسف كمال رمضان حميده</t>
+  </si>
+  <si>
+    <t>يوسف محمد بدير علي بدير</t>
+  </si>
+  <si>
+    <t>يوسف محمد بكر مرسي</t>
+  </si>
+  <si>
+    <t>م. محمد جابر خليل</t>
+  </si>
+  <si>
+    <t>mjaberkhalil@eelu.edu.eg</t>
+  </si>
+  <si>
+    <t>أحمد شعبان توفيق عبدالواحد</t>
+  </si>
+  <si>
+    <t>أحمد علاء عبدالفتاح صادق</t>
+  </si>
+  <si>
+    <t>أحمد محمد السيد عبدالفتاح</t>
+  </si>
+  <si>
+    <t>أحمد محمد عبدالحكيم العمرى</t>
+  </si>
+  <si>
+    <t>أحمد محمد معوض محمد</t>
+  </si>
+  <si>
+    <t>أدم خالد عبدالجواد متولى</t>
+  </si>
+  <si>
+    <t>أسامة محمد أحمد عبدالحفيظ</t>
+  </si>
+  <si>
+    <t>أسامة محمود صالح عبد الجواد</t>
+  </si>
+  <si>
+    <t>أشرف عبدالحميد السيد الحلفاوى</t>
+  </si>
+  <si>
+    <t>أمنية محمد محمد محمد عرفه</t>
+  </si>
+  <si>
+    <t>أميرة رجب محمود جابر</t>
+  </si>
+  <si>
+    <t>أيمن عبدالرحمن السيد عبدالرازق</t>
+  </si>
+  <si>
+    <t>إسراء أحمد محمود عبد العظيم</t>
+  </si>
+  <si>
+    <t>إهداء اسامه محمد نور</t>
+  </si>
+  <si>
+    <t>إهداء سعيد عبدالباقي منصور</t>
+  </si>
+  <si>
+    <t>إيثار إسماعيل صالح إسماعيل محمد</t>
+  </si>
+  <si>
+    <t>ابانوب ايمن سامي خليل صالح</t>
+  </si>
+  <si>
+    <t>ابانوب ايمن صبحي كامل</t>
+  </si>
+  <si>
+    <t>ابانوب عبيد ثابت داود</t>
+  </si>
+  <si>
+    <t>ابتسام عبد العليم رفاعي جمعة</t>
+  </si>
+  <si>
+    <t>ابرار عبدالله عبدالعاطي علي</t>
+  </si>
+  <si>
+    <t>ابرام ايهاب نعيم يعقوب</t>
+  </si>
+  <si>
+    <t>ابراهيم احمد رشاد شعبان</t>
+  </si>
+  <si>
+    <t>ابراهيم ايوب توفيق ايوب</t>
+  </si>
+  <si>
+    <t>ابراهيم جمال السيد ابراهيم</t>
+  </si>
+  <si>
+    <t>ابراهيم محسن محمد عبد الله حمد</t>
+  </si>
+  <si>
+    <t>احمد امين رشاد امين</t>
+  </si>
+  <si>
+    <t>احمد ايمن حمدي عيسى</t>
+  </si>
+  <si>
+    <t>احمد بليغ حمدي عبدالله</t>
+  </si>
+  <si>
+    <t>احمد جمال محمد احمد</t>
+  </si>
+  <si>
+    <t>احمد حجازي جبر عبدالله</t>
+  </si>
+  <si>
+    <t>احمد حسن احمد حميده</t>
+  </si>
+  <si>
+    <t>احمد حمدي السيد علي</t>
+  </si>
+  <si>
+    <t>احمد سامح محمد حافظ</t>
+  </si>
+  <si>
+    <t>احمد سيد اسماعيل عجاب</t>
+  </si>
+  <si>
+    <t>احمد شريف عبدالغفار حافظ</t>
+  </si>
+  <si>
+    <t>احمد شعبان عبدالله شافعي</t>
+  </si>
+  <si>
+    <t>احمد شوقي عيد عبدالمقصود</t>
+  </si>
+  <si>
+    <t>احمد صالح جمعه عبدالجيد</t>
+  </si>
+  <si>
+    <t>احمد عبدالله محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد عصام حمدى محمد</t>
+  </si>
+  <si>
+    <t>احمد على احمد مراد</t>
+  </si>
+  <si>
+    <t>احمد عمار السيد عبدالقادر</t>
+  </si>
+  <si>
+    <t>احمد محمد عبدالتواب عبدالباقي</t>
+  </si>
+  <si>
+    <t>احمد محمد عشيري صالح</t>
+  </si>
+  <si>
+    <t>احمد محمد علي محمد</t>
+  </si>
+  <si>
+    <t>احمد محمود جمعه عبدالجيد</t>
+  </si>
+  <si>
+    <t>احمد محمود حسن علي محمد</t>
+  </si>
+  <si>
+    <t>احمد محمود عبدالعاطى محمود</t>
+  </si>
+  <si>
+    <t>احمد محمود محمد صفوت</t>
+  </si>
+  <si>
+    <t>احمد ناصر روبى عبدالجواد</t>
+  </si>
+  <si>
+    <t>احمد هشام احمد مصطفى</t>
+  </si>
+  <si>
+    <t>ادهم احمد محمود محمود عبد الهادي</t>
+  </si>
+  <si>
+    <t>اسماء احمد صلاح احمد</t>
+  </si>
+  <si>
+    <t>ذياد كريم حنفي عبد الرحمن</t>
+  </si>
+  <si>
+    <t>رأفت اشرف كليب عبدالمجيد</t>
+  </si>
+  <si>
+    <t>محمد كمال ابراهيم السيد</t>
+  </si>
+  <si>
+    <t>محمد مجدى احمد عبدالحميد</t>
+  </si>
+  <si>
+    <t>محمد مجدي شحات فرج</t>
+  </si>
+  <si>
+    <t>محمد محسن السيد كامل عثمان</t>
+  </si>
+  <si>
+    <t>محمد محسن مصطفى عبدالعظيم</t>
+  </si>
+  <si>
+    <t>محمد محمود احمد محمد</t>
+  </si>
+  <si>
+    <t>محمد محمود عبدالرحمن أحمد</t>
+  </si>
+  <si>
+    <t>محمد محمود عبدالرحمن السيد</t>
+  </si>
+  <si>
+    <t>محمد ناصر محمد عبدالباقى</t>
+  </si>
+  <si>
+    <t>محمد هاني توفيق علي</t>
+  </si>
+  <si>
+    <t>محمد ياسر محمد سلام</t>
+  </si>
+  <si>
+    <t>محمد يسري محمد رمضان</t>
+  </si>
+  <si>
+    <t>محمود احمد طه السيد</t>
+  </si>
+  <si>
+    <t>محمود جمال حسين ابو بكر محمد</t>
+  </si>
+  <si>
+    <t>محمود خالد محمود عبدالمجيد</t>
+  </si>
+  <si>
+    <t>محمود خيرى رمضان قطب</t>
+  </si>
+  <si>
+    <t>محمود رجب جمعه محمد</t>
+  </si>
+  <si>
+    <t>محمود عثمان جابر عثمان</t>
+  </si>
+  <si>
+    <t>محمود قطب محمود سيف</t>
+  </si>
+  <si>
+    <t>محمود محمد صالح عويضه</t>
+  </si>
+  <si>
+    <t>محمود محمد عبد الصادق عبد المجيد</t>
+  </si>
+  <si>
+    <t>محمود نادى محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>مدحت ممدوح احمد خميس</t>
+  </si>
+  <si>
+    <t>مروان حسن كمال الدين عبدالقوي فرج</t>
+  </si>
+  <si>
+    <t>مروان ربيع عيد عبد الحفيظ</t>
+  </si>
+  <si>
+    <t>مروان محمد وجيه عبدالعظيم</t>
+  </si>
+  <si>
+    <t>مريم ايمن احمد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>مريم حسن كمال الدين</t>
+  </si>
+  <si>
+    <t>مريم شوقي عطيه محمد</t>
+  </si>
+  <si>
+    <t>مريم علي السيد محمد</t>
+  </si>
+  <si>
+    <t>مريم فادي فؤاد وهبه</t>
+  </si>
+  <si>
+    <t>مريم محمد علي عباس</t>
+  </si>
+  <si>
+    <t>مريم محمود سامي حسين</t>
+  </si>
+  <si>
+    <t>منه الله مصطفي محمود السيد محمود</t>
+  </si>
+  <si>
+    <t>منه محمد سيد محمد السيد الدش</t>
+  </si>
+  <si>
+    <t>م. آلاء يوســـــــف</t>
+  </si>
+  <si>
+    <t>ayoussefsiddiq@eelu.edu.eg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4013,8 +4556,135 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4027,8 +4697,181 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -4036,10 +4879,158 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4053,9 +5044,50 @@
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="43">
+    <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="24" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="32" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="36" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="21" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="25" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="29" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="33" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="37" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="41" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="26" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="30" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="34" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="38" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="42" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="19" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="23" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="27" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="31" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="35" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="8" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="12" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="14" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="17" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="7" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="3" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="4" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="5" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Input" xfId="10" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="13" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="9" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="16" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="11" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="2" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4387,7 +5419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507AC9FC-3305-4A8E-963E-423E46E70006}">
-  <dimension ref="A1:D1279"/>
+  <dimension ref="A1:D1456"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -22300,6 +23332,2484 @@
       </c>
       <c r="D1279" s="2" t="s">
         <v>1312</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1280" s="1">
+        <v>2201972</v>
+      </c>
+      <c r="B1280" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C1280" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1280" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1281" s="1">
+        <v>2400363</v>
+      </c>
+      <c r="B1281" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C1281" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1281" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1282" s="1">
+        <v>2403878</v>
+      </c>
+      <c r="B1282" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C1282" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1282" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1283" s="1">
+        <v>2400534</v>
+      </c>
+      <c r="B1283" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C1283" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1283" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1284" s="1">
+        <v>2202142</v>
+      </c>
+      <c r="B1284" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C1284" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1284" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1285" s="1">
+        <v>2300240</v>
+      </c>
+      <c r="B1285" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C1285" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1285" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1286" s="1">
+        <v>2300242</v>
+      </c>
+      <c r="B1286" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C1286" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1286" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1287" s="1">
+        <v>2302288</v>
+      </c>
+      <c r="B1287" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C1287" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1287" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1288" s="1">
+        <v>2500500</v>
+      </c>
+      <c r="B1288" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C1288" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1288" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1289" s="1">
+        <v>2302283</v>
+      </c>
+      <c r="B1289" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C1289" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1289" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1290" s="1">
+        <v>2301883</v>
+      </c>
+      <c r="B1290" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C1290" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1290" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1291" s="1">
+        <v>2301520</v>
+      </c>
+      <c r="B1291" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C1291" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1291" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1292" s="1">
+        <v>2500148</v>
+      </c>
+      <c r="B1292" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C1292" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1292" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1293" s="1">
+        <v>2202065</v>
+      </c>
+      <c r="B1293" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C1293" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1293" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1294" s="1">
+        <v>2202037</v>
+      </c>
+      <c r="B1294" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C1294" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1294" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1295" s="1">
+        <v>2301954</v>
+      </c>
+      <c r="B1295" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C1295" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1295" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1296" s="1">
+        <v>2202050</v>
+      </c>
+      <c r="B1296" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C1296" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1296" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1297" s="1">
+        <v>2300244</v>
+      </c>
+      <c r="B1297" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C1297" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1297" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1298" s="1">
+        <v>2200913</v>
+      </c>
+      <c r="B1298" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C1298" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1298" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1299" s="1">
+        <v>2301434</v>
+      </c>
+      <c r="B1299" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C1299" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1299" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1300" s="1">
+        <v>2202036</v>
+      </c>
+      <c r="B1300" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C1300" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1300" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1301" s="1">
+        <v>2500158</v>
+      </c>
+      <c r="B1301" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C1301" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1301" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1302" s="1">
+        <v>2500532</v>
+      </c>
+      <c r="B1302" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C1302" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1302" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1303" s="1">
+        <v>2302023</v>
+      </c>
+      <c r="B1303" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C1303" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1303" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1304" s="1">
+        <v>2202024</v>
+      </c>
+      <c r="B1304" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C1304" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1304" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1305" s="1">
+        <v>2401368</v>
+      </c>
+      <c r="B1305" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C1305" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1305" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1306" s="1">
+        <v>2400344</v>
+      </c>
+      <c r="B1306" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C1306" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1306" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1307" s="1">
+        <v>2201966</v>
+      </c>
+      <c r="B1307" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C1307" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1307" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1308" s="1">
+        <v>2301610</v>
+      </c>
+      <c r="B1308" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C1308" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1308" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1309" s="1">
+        <v>2400393</v>
+      </c>
+      <c r="B1309" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C1309" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1309" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1310" s="1">
+        <v>2300233</v>
+      </c>
+      <c r="B1310" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C1310" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1310" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1311" s="1">
+        <v>2400957</v>
+      </c>
+      <c r="B1311" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C1311" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1311" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1312" s="1">
+        <v>2202013</v>
+      </c>
+      <c r="B1312" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C1312" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1312" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1313" s="1">
+        <v>2300065</v>
+      </c>
+      <c r="B1313" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C1313" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1313" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1314" s="1">
+        <v>2300058</v>
+      </c>
+      <c r="B1314" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C1314" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1314" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1315" s="1">
+        <v>2300340</v>
+      </c>
+      <c r="B1315" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C1315" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1315" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1316" s="1">
+        <v>2403017</v>
+      </c>
+      <c r="B1316" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C1316" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1316" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1317" s="1">
+        <v>2201988</v>
+      </c>
+      <c r="B1317" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C1317" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1317" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1318" s="1">
+        <v>2202017</v>
+      </c>
+      <c r="B1318" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C1318" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1318" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1319" s="1">
+        <v>2300296</v>
+      </c>
+      <c r="B1319" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C1319" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1319" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1320" s="1">
+        <v>2201986</v>
+      </c>
+      <c r="B1320" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C1320" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1320" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1321" s="1">
+        <v>2400365</v>
+      </c>
+      <c r="B1321" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C1321" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1321" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1322" s="1">
+        <v>2400330</v>
+      </c>
+      <c r="B1322" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C1322" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1322" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1323" s="1">
+        <v>2201968</v>
+      </c>
+      <c r="B1323" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C1323" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1323" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1324" s="1">
+        <v>2202002</v>
+      </c>
+      <c r="B1324" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C1324" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1324" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1325" s="1">
+        <v>2301874</v>
+      </c>
+      <c r="B1325" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C1325" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1325" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1326" s="1">
+        <v>2201979</v>
+      </c>
+      <c r="B1326" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C1326" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1326" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1327" s="1">
+        <v>2400434</v>
+      </c>
+      <c r="B1327" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C1327" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1327" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1328" s="1">
+        <v>2302280</v>
+      </c>
+      <c r="B1328" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C1328" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1328" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1329" s="1">
+        <v>2300226</v>
+      </c>
+      <c r="B1329" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C1329" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1329" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1330" s="1">
+        <v>2300292</v>
+      </c>
+      <c r="B1330" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C1330" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1330" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1331" s="1">
+        <v>2201985</v>
+      </c>
+      <c r="B1331" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C1331" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1331" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1332" s="1">
+        <v>2400352</v>
+      </c>
+      <c r="B1332" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1332" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1332" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1333" s="1">
+        <v>2400488</v>
+      </c>
+      <c r="B1333" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C1333" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1333" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1334" s="1">
+        <v>2401635</v>
+      </c>
+      <c r="B1334" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C1334" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1334" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1335" s="1">
+        <v>2201960</v>
+      </c>
+      <c r="B1335" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C1335" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1335" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1336" s="1">
+        <v>2300303</v>
+      </c>
+      <c r="B1336" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C1336" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1336" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1337" s="1">
+        <v>2302769</v>
+      </c>
+      <c r="B1337" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C1337" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1337" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1338" s="1">
+        <v>2302084</v>
+      </c>
+      <c r="B1338" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C1338" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1338" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1339" s="1">
+        <v>2201980</v>
+      </c>
+      <c r="B1339" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C1339" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1339" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1340" s="1">
+        <v>2201977</v>
+      </c>
+      <c r="B1340" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C1340" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1340" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1341" s="1">
+        <v>2401969</v>
+      </c>
+      <c r="B1341" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C1341" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1341" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1342" s="1">
+        <v>2401637</v>
+      </c>
+      <c r="B1342" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C1342" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1342" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1343" s="1">
+        <v>2301862</v>
+      </c>
+      <c r="B1343" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C1343" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1343" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1344" s="1">
+        <v>2300323</v>
+      </c>
+      <c r="B1344" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C1344" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1344" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1345" s="1">
+        <v>2400400</v>
+      </c>
+      <c r="B1345" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C1345" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1345" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1346" s="1">
+        <v>2400489</v>
+      </c>
+      <c r="B1346" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C1346" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1346" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1347" s="1">
+        <v>2400514</v>
+      </c>
+      <c r="B1347" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C1347" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1347" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1348" s="1">
+        <v>2400397</v>
+      </c>
+      <c r="B1348" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C1348" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1348" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1349" s="1">
+        <v>2400360</v>
+      </c>
+      <c r="B1349" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C1349" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1349" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1350" s="1">
+        <v>2400479</v>
+      </c>
+      <c r="B1350" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C1350" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1350" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1351" s="1">
+        <v>2400420</v>
+      </c>
+      <c r="B1351" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C1351" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1351" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1352" s="1">
+        <v>2400251</v>
+      </c>
+      <c r="B1352" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C1352" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1352" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1353" s="1">
+        <v>2300214</v>
+      </c>
+      <c r="B1353" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C1353" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1353" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1354" s="1">
+        <v>2400006</v>
+      </c>
+      <c r="B1354" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C1354" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1354" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1355" s="1">
+        <v>2300304</v>
+      </c>
+      <c r="B1355" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C1355" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1355" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1356" s="1">
+        <v>2302223</v>
+      </c>
+      <c r="B1356" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C1356" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1356" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1357" s="1">
+        <v>2400525</v>
+      </c>
+      <c r="B1357" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C1357" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1357" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1358" s="1">
+        <v>2400343</v>
+      </c>
+      <c r="B1358" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C1358" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1358" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1359" s="1">
+        <v>2400398</v>
+      </c>
+      <c r="B1359" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C1359" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1359" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1360" s="1">
+        <v>2302004</v>
+      </c>
+      <c r="B1360" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C1360" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1360" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1361" s="1">
+        <v>2301475</v>
+      </c>
+      <c r="B1361" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C1361" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1361" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1362" s="1">
+        <v>2400486</v>
+      </c>
+      <c r="B1362" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C1362" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1362" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1363" s="1">
+        <v>2301973</v>
+      </c>
+      <c r="B1363" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C1363" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1363" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1364" s="1">
+        <v>2403876</v>
+      </c>
+      <c r="B1364" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C1364" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1364" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1365" s="1">
+        <v>2301455</v>
+      </c>
+      <c r="B1365" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C1365" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D1365" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1366" s="1">
+        <v>2400475</v>
+      </c>
+      <c r="B1366" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C1366" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1366" s="2" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1367" s="1">
+        <v>2400402</v>
+      </c>
+      <c r="B1367" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C1367" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1367" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1368" s="1">
+        <v>2300069</v>
+      </c>
+      <c r="B1368" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C1368" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1368" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1369" s="1">
+        <v>2400303</v>
+      </c>
+      <c r="B1369" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C1369" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1369" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1370" s="1">
+        <v>2301972</v>
+      </c>
+      <c r="B1370" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C1370" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1370" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1371" s="1">
+        <v>2400305</v>
+      </c>
+      <c r="B1371" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C1371" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1371" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1372" s="1">
+        <v>2402271</v>
+      </c>
+      <c r="B1372" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C1372" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1372" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1373" s="1">
+        <v>2401618</v>
+      </c>
+      <c r="B1373" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C1373" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1373" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1374" s="1">
+        <v>2400091</v>
+      </c>
+      <c r="B1374" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C1374" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1374" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1375" s="1">
+        <v>2300333</v>
+      </c>
+      <c r="B1375" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C1375" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1375" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1376" s="1">
+        <v>2401371</v>
+      </c>
+      <c r="B1376" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C1376" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1376" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1377" s="1">
+        <v>2302087</v>
+      </c>
+      <c r="B1377" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C1377" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1377" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1378" s="1">
+        <v>2302006</v>
+      </c>
+      <c r="B1378" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C1378" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1378" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1379" s="1">
+        <v>2400355</v>
+      </c>
+      <c r="B1379" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C1379" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1379" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1380" s="1">
+        <v>2400055</v>
+      </c>
+      <c r="B1380" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C1380" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1380" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1381" s="1">
+        <v>2301976</v>
+      </c>
+      <c r="B1381" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C1381" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1381" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1382" s="1">
+        <v>2302644</v>
+      </c>
+      <c r="B1382" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C1382" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1382" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1383" s="1">
+        <v>2400500</v>
+      </c>
+      <c r="B1383" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1383" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1383" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1384" s="1">
+        <v>2400453</v>
+      </c>
+      <c r="B1384" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C1384" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1384" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1385" s="1">
+        <v>2300720</v>
+      </c>
+      <c r="B1385" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C1385" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1385" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1386" s="1">
+        <v>2202009</v>
+      </c>
+      <c r="B1386" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C1386" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1386" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1387" s="1">
+        <v>2300316</v>
+      </c>
+      <c r="B1387" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C1387" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1387" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1388" s="1">
+        <v>2302021</v>
+      </c>
+      <c r="B1388" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C1388" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1388" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1389" s="1">
+        <v>2300318</v>
+      </c>
+      <c r="B1389" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C1389" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1389" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1390" s="1">
+        <v>2302002</v>
+      </c>
+      <c r="B1390" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C1390" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1390" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1391" s="1">
+        <v>2400142</v>
+      </c>
+      <c r="B1391" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C1391" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1391" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1392" s="1">
+        <v>2401367</v>
+      </c>
+      <c r="B1392" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C1392" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1392" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1393" s="1">
+        <v>2403877</v>
+      </c>
+      <c r="B1393" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C1393" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1393" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1394" s="1">
+        <v>2301513</v>
+      </c>
+      <c r="B1394" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C1394" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1394" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1395" s="1">
+        <v>2202086</v>
+      </c>
+      <c r="B1395" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C1395" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1395" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1396" s="1">
+        <v>2400374</v>
+      </c>
+      <c r="B1396" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C1396" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1396" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1397" s="1">
+        <v>2400336</v>
+      </c>
+      <c r="B1397" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C1397" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1397" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1398" s="1">
+        <v>2302010</v>
+      </c>
+      <c r="B1398" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C1398" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1398" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1399" s="1">
+        <v>2400410</v>
+      </c>
+      <c r="B1399" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C1399" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1399" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1400" s="1">
+        <v>2401611</v>
+      </c>
+      <c r="B1400" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C1400" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1400" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1401" s="1">
+        <v>2400437</v>
+      </c>
+      <c r="B1401" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C1401" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1401" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1402" s="1">
+        <v>2400845</v>
+      </c>
+      <c r="B1402" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C1402" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1402" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1403" s="1">
+        <v>2401615</v>
+      </c>
+      <c r="B1403" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C1403" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1403" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1404" s="1">
+        <v>2302101</v>
+      </c>
+      <c r="B1404" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C1404" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1404" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1405" s="1">
+        <v>2401352</v>
+      </c>
+      <c r="B1405" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C1405" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1405" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1406" s="1">
+        <v>2401636</v>
+      </c>
+      <c r="B1406" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C1406" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1406" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1407" s="1">
+        <v>2400474</v>
+      </c>
+      <c r="B1407" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C1407" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1407" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1408" s="1">
+        <v>2400485</v>
+      </c>
+      <c r="B1408" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C1408" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1408" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1409" s="1">
+        <v>2301970</v>
+      </c>
+      <c r="B1409" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C1409" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1409" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1410" s="1">
+        <v>2202080</v>
+      </c>
+      <c r="B1410" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C1410" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1410" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1411" s="1">
+        <v>2403879</v>
+      </c>
+      <c r="B1411" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C1411" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1411" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1412" s="1">
+        <v>2401621</v>
+      </c>
+      <c r="B1412" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C1412" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1412" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1413" s="1">
+        <v>2401386</v>
+      </c>
+      <c r="B1413" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C1413" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1413" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1414" s="1">
+        <v>2400481</v>
+      </c>
+      <c r="B1414" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C1414" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1414" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1415" s="1">
+        <v>2300306</v>
+      </c>
+      <c r="B1415" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C1415" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1415" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1416" s="1">
+        <v>2401385</v>
+      </c>
+      <c r="B1416" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C1416" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1416" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1417" s="1">
+        <v>2300299</v>
+      </c>
+      <c r="B1417" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C1417" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1417" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1418" s="1">
+        <v>2400501</v>
+      </c>
+      <c r="B1418" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C1418" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1418" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1419" s="1">
+        <v>2200725</v>
+      </c>
+      <c r="B1419" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C1419" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1419" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1420" s="1">
+        <v>2400518</v>
+      </c>
+      <c r="B1420" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C1420" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1420" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1421" s="1">
+        <v>2200840</v>
+      </c>
+      <c r="B1421" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C1421" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1421" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1422" s="1">
+        <v>2300174</v>
+      </c>
+      <c r="B1422" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C1422" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1422" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1423" s="1">
+        <v>2302028</v>
+      </c>
+      <c r="B1423" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C1423" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1423" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1424" s="1">
+        <v>2500196</v>
+      </c>
+      <c r="B1424" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C1424" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1424" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1425" s="1">
+        <v>2500453</v>
+      </c>
+      <c r="B1425" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C1425" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1425" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1426" s="1">
+        <v>2301163</v>
+      </c>
+      <c r="B1426" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C1426" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1426" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1427" s="1">
+        <v>2202033</v>
+      </c>
+      <c r="B1427" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C1427" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1427" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1428" s="1">
+        <v>2502178</v>
+      </c>
+      <c r="B1428" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C1428" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1428" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1429" s="1">
+        <v>2300857</v>
+      </c>
+      <c r="B1429" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C1429" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1429" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1430" s="1">
+        <v>2302287</v>
+      </c>
+      <c r="B1430" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C1430" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1430" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1431" s="1">
+        <v>2500908</v>
+      </c>
+      <c r="B1431" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C1431" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1431" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1432" s="1">
+        <v>2200914</v>
+      </c>
+      <c r="B1432" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C1432" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1432" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1433" s="1">
+        <v>2300234</v>
+      </c>
+      <c r="B1433" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C1433" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1433" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1434" s="1">
+        <v>2500221</v>
+      </c>
+      <c r="B1434" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C1434" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1434" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1435" s="1">
+        <v>2301644</v>
+      </c>
+      <c r="B1435" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C1435" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1435" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1436" s="1">
+        <v>2500009</v>
+      </c>
+      <c r="B1436" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C1436" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1436" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1437" s="1">
+        <v>2202064</v>
+      </c>
+      <c r="B1437" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C1437" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1437" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1438" s="1">
+        <v>2300102</v>
+      </c>
+      <c r="B1438" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C1438" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1438" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1439" s="1">
+        <v>2302034</v>
+      </c>
+      <c r="B1439" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C1439" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1439" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1440" s="1">
+        <v>2502657</v>
+      </c>
+      <c r="B1440" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C1440" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1440" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1441" s="1">
+        <v>2301912</v>
+      </c>
+      <c r="B1441" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C1441" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1441" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1442" s="1">
+        <v>2500522</v>
+      </c>
+      <c r="B1442" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C1442" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1442" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1443" s="1">
+        <v>2501255</v>
+      </c>
+      <c r="B1443" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C1443" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1443" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1444" s="1">
+        <v>2500013</v>
+      </c>
+      <c r="B1444" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C1444" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1444" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1445" s="1">
+        <v>2500537</v>
+      </c>
+      <c r="B1445" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C1445" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1445" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1446" s="1">
+        <v>2500210</v>
+      </c>
+      <c r="B1446" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C1446" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1446" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1447" s="1">
+        <v>2500918</v>
+      </c>
+      <c r="B1447" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C1447" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1447" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1448" s="1">
+        <v>2301433</v>
+      </c>
+      <c r="B1448" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C1448" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1448" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1449" s="1">
+        <v>2500539</v>
+      </c>
+      <c r="B1449" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C1449" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1449" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1450" s="1">
+        <v>2502172</v>
+      </c>
+      <c r="B1450" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C1450" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1450" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1451" s="1">
+        <v>2500471</v>
+      </c>
+      <c r="B1451" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C1451" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1451" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1452" s="1">
+        <v>2500541</v>
+      </c>
+      <c r="B1452" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C1452" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1452" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1453" s="1">
+        <v>2300342</v>
+      </c>
+      <c r="B1453" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C1453" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1453" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1454" s="1">
+        <v>2500456</v>
+      </c>
+      <c r="B1454" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C1454" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1454" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1455" s="1">
+        <v>2201997</v>
+      </c>
+      <c r="B1455" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C1455" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1455" s="1" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1456" s="1">
+        <v>2201996</v>
+      </c>
+      <c r="B1456" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C1456" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1456" s="1" t="s">
+        <v>1494</v>
       </c>
     </row>
   </sheetData>
@@ -23408,6 +26918,93 @@
     <hyperlink ref="D1102" r:id="rId1101" xr:uid="{14BC1FA7-CB78-415C-894A-BEB16C8D5A9A}"/>
     <hyperlink ref="D1188" r:id="rId1102" xr:uid="{EAFD5C1A-0156-4D8E-9C11-1413314FB42D}"/>
     <hyperlink ref="D1189:D1279" r:id="rId1103" display="rewais@eelu.edu.eg" xr:uid="{E8B709D3-B661-4C9A-A8BA-45D694772EAF}"/>
+    <hyperlink ref="D1280" r:id="rId1104" xr:uid="{6E1E399C-AB73-4BE8-9AA0-CEFE294FC175}"/>
+    <hyperlink ref="D1281" r:id="rId1105" xr:uid="{A3A85950-E942-4B5A-8876-304EBE7E63BC}"/>
+    <hyperlink ref="D1282" r:id="rId1106" xr:uid="{3B046432-ABAA-49BD-A6DE-66A19F444729}"/>
+    <hyperlink ref="D1283" r:id="rId1107" xr:uid="{E9755CDA-F7A7-488C-BCA5-47C80DF996AC}"/>
+    <hyperlink ref="D1284" r:id="rId1108" xr:uid="{4687BBAA-E1C8-432D-82D2-EAE25C1DE596}"/>
+    <hyperlink ref="D1285" r:id="rId1109" xr:uid="{EA1E0FFE-6192-4A0F-A3C8-FD76B8836805}"/>
+    <hyperlink ref="D1286" r:id="rId1110" xr:uid="{CC227C29-E034-4656-8F22-01A4211E07A4}"/>
+    <hyperlink ref="D1287" r:id="rId1111" xr:uid="{81EBC45E-96A2-492C-9DA5-76505341D849}"/>
+    <hyperlink ref="D1288" r:id="rId1112" xr:uid="{0BF85D00-5256-4ABC-B9B8-9B0636965C94}"/>
+    <hyperlink ref="D1289" r:id="rId1113" xr:uid="{16D21406-60E5-4229-ACCF-00DDC3E0C5F1}"/>
+    <hyperlink ref="D1290" r:id="rId1114" xr:uid="{FA32E87D-6EBD-464F-B8AD-2D8DB669099F}"/>
+    <hyperlink ref="D1291" r:id="rId1115" xr:uid="{1D5144B6-AA2E-471C-89EC-F3E1D654367D}"/>
+    <hyperlink ref="D1292" r:id="rId1116" xr:uid="{F32CC32A-4330-43F4-B1D3-066F4A7C99F1}"/>
+    <hyperlink ref="D1293" r:id="rId1117" xr:uid="{AC557563-2E1D-4EDD-AE74-D977DD5CA594}"/>
+    <hyperlink ref="D1294" r:id="rId1118" xr:uid="{4DB7AB20-1869-4A9B-A6DB-6A1EE37707EB}"/>
+    <hyperlink ref="D1295" r:id="rId1119" xr:uid="{E270D7F0-DA6F-416E-96FF-E8E7A838A0C2}"/>
+    <hyperlink ref="D1296" r:id="rId1120" xr:uid="{DD023383-2228-4E2F-93A6-BDA4960F53AC}"/>
+    <hyperlink ref="D1297" r:id="rId1121" xr:uid="{608F6958-237C-457B-9A5A-C0FBE042CB50}"/>
+    <hyperlink ref="D1298" r:id="rId1122" xr:uid="{5F85F554-59C9-4302-B9CF-671405F7E150}"/>
+    <hyperlink ref="D1299" r:id="rId1123" xr:uid="{BC2B1A0A-40F8-4184-91E3-EA02359B4202}"/>
+    <hyperlink ref="D1300" r:id="rId1124" xr:uid="{2439B924-5134-4A2C-AD06-695B13118305}"/>
+    <hyperlink ref="D1301" r:id="rId1125" xr:uid="{A3C71242-727C-4498-85C3-D08BF0000A82}"/>
+    <hyperlink ref="D1302" r:id="rId1126" xr:uid="{4AA6667E-8C9F-4BA8-BD35-75650E3E8B17}"/>
+    <hyperlink ref="D1303" r:id="rId1127" xr:uid="{5329EBBE-1572-4F9C-902F-3F2B4E9B6ACD}"/>
+    <hyperlink ref="D1304" r:id="rId1128" xr:uid="{535E29CA-BDAF-4C27-AE8F-C63C8AF84C94}"/>
+    <hyperlink ref="D1305" r:id="rId1129" xr:uid="{6DF4EF3B-CFF6-4FD8-9F9F-4314989EE360}"/>
+    <hyperlink ref="D1306" r:id="rId1130" xr:uid="{31A421FF-57D8-43DC-8055-ED467FC54B53}"/>
+    <hyperlink ref="D1307" r:id="rId1131" xr:uid="{63B4F141-3DAF-455F-B76C-8DEA8E0C33FD}"/>
+    <hyperlink ref="D1308" r:id="rId1132" xr:uid="{A0BB2A9B-2165-4383-9223-1FA55ACF2A5C}"/>
+    <hyperlink ref="D1309" r:id="rId1133" xr:uid="{5ABB63B3-E29D-4B4E-893C-20A092916480}"/>
+    <hyperlink ref="D1310" r:id="rId1134" xr:uid="{BE522FEC-1DFF-41D8-89E9-44460F457420}"/>
+    <hyperlink ref="D1311" r:id="rId1135" xr:uid="{C51DFA0E-A252-4435-9644-5C2EB7C66016}"/>
+    <hyperlink ref="D1312" r:id="rId1136" xr:uid="{5BCC605A-74FA-4AF4-94E3-710BD990D49C}"/>
+    <hyperlink ref="D1313" r:id="rId1137" xr:uid="{D0655C10-DA3F-4AD0-94CE-B9ACC458E787}"/>
+    <hyperlink ref="D1314" r:id="rId1138" xr:uid="{8B9B2425-6BC3-48BE-9B9B-78105F13B9E3}"/>
+    <hyperlink ref="D1315" r:id="rId1139" xr:uid="{FCB1E27C-98C9-446A-AD12-02086141A051}"/>
+    <hyperlink ref="D1316" r:id="rId1140" xr:uid="{ACB86EE7-4841-457E-99DE-D9CDB8EB2EE3}"/>
+    <hyperlink ref="D1317" r:id="rId1141" xr:uid="{D68164BA-CE07-4070-8F83-1C67BCFC1770}"/>
+    <hyperlink ref="D1318" r:id="rId1142" xr:uid="{7DC3F584-D49F-408B-8306-16B2792B984A}"/>
+    <hyperlink ref="D1319" r:id="rId1143" xr:uid="{A835C614-F152-4461-AD08-B13D2A131059}"/>
+    <hyperlink ref="D1320" r:id="rId1144" xr:uid="{07A60F1B-C890-4171-9DDE-7BE637C21B7D}"/>
+    <hyperlink ref="D1321" r:id="rId1145" xr:uid="{F980ACAB-B5D8-46B2-ABE5-ECD75EE4B046}"/>
+    <hyperlink ref="D1322" r:id="rId1146" xr:uid="{7B9459AB-1D32-40D3-A77A-CDCE51785007}"/>
+    <hyperlink ref="D1323" r:id="rId1147" xr:uid="{AA93DE84-40A0-47A1-9BCD-D556B29EF1C8}"/>
+    <hyperlink ref="D1324" r:id="rId1148" xr:uid="{B2CF3C36-2AC9-4A9B-821A-4213A0E11BEC}"/>
+    <hyperlink ref="D1325" r:id="rId1149" xr:uid="{10F07CC9-6919-42BA-AA2D-4781A6CC975F}"/>
+    <hyperlink ref="D1326" r:id="rId1150" xr:uid="{48E9702B-0CC9-45D3-BBE4-FD22EF98CBFA}"/>
+    <hyperlink ref="D1327" r:id="rId1151" xr:uid="{D8B63292-40E4-4ECF-AF69-F75515AC61FB}"/>
+    <hyperlink ref="D1328" r:id="rId1152" xr:uid="{05DA60D2-1864-40F8-8849-2994DD38BD3B}"/>
+    <hyperlink ref="D1329" r:id="rId1153" xr:uid="{706C336E-DF07-4A5A-B00A-32CB5B5EAB15}"/>
+    <hyperlink ref="D1330" r:id="rId1154" xr:uid="{3410B1E0-F37F-4F0C-BB07-64490B06B1E6}"/>
+    <hyperlink ref="D1331" r:id="rId1155" xr:uid="{D649DED5-25FF-4DE5-95D2-575E8AD55053}"/>
+    <hyperlink ref="D1332" r:id="rId1156" xr:uid="{B494FD71-E20C-42A7-8EBD-A7E46FDD03A6}"/>
+    <hyperlink ref="D1333" r:id="rId1157" xr:uid="{8D6A9863-517F-4797-9CB0-5B07CA095C44}"/>
+    <hyperlink ref="D1334" r:id="rId1158" xr:uid="{24740C7E-2270-4042-8A93-540EFDECA29E}"/>
+    <hyperlink ref="D1335" r:id="rId1159" xr:uid="{85571103-194A-47D7-B7C4-C263E8B7B18B}"/>
+    <hyperlink ref="D1336" r:id="rId1160" xr:uid="{ABA0CC08-227F-415D-84E4-26318A0FDC36}"/>
+    <hyperlink ref="D1337" r:id="rId1161" xr:uid="{8455995E-1AA5-4ADD-ADD3-92468C7ADE33}"/>
+    <hyperlink ref="D1338" r:id="rId1162" xr:uid="{110776B7-97D6-4AE5-81A3-E2694FCFFC4F}"/>
+    <hyperlink ref="D1339" r:id="rId1163" xr:uid="{220888B3-4A98-420D-850E-8299A95E3641}"/>
+    <hyperlink ref="D1340" r:id="rId1164" xr:uid="{61893E58-B18C-4DC5-B8F0-3190E9BFA3C6}"/>
+    <hyperlink ref="D1341" r:id="rId1165" xr:uid="{F164C166-DEC7-4E1C-B7BF-AB4A357D9D38}"/>
+    <hyperlink ref="D1342" r:id="rId1166" xr:uid="{B0CB12EC-C87F-46A6-A97B-D26C83331FC8}"/>
+    <hyperlink ref="D1343" r:id="rId1167" xr:uid="{492DA29A-D013-4571-861C-097879D9063D}"/>
+    <hyperlink ref="D1344" r:id="rId1168" xr:uid="{D948420A-508B-461F-A6EE-F73FFF0F5303}"/>
+    <hyperlink ref="D1345" r:id="rId1169" xr:uid="{ABAF5627-0735-40A5-A836-11A63E3FF802}"/>
+    <hyperlink ref="D1346" r:id="rId1170" xr:uid="{28F4E617-679C-4405-96D3-E9761A3AF450}"/>
+    <hyperlink ref="D1347" r:id="rId1171" xr:uid="{9EB35647-3F1D-45AD-AF31-DA8BE7CAC202}"/>
+    <hyperlink ref="D1348" r:id="rId1172" xr:uid="{55D52B36-7681-489D-AAB8-2AED836995DD}"/>
+    <hyperlink ref="D1349" r:id="rId1173" xr:uid="{C47F6A70-7C8B-4A65-8421-1442C4BD5AB1}"/>
+    <hyperlink ref="D1350" r:id="rId1174" xr:uid="{E5075555-1DB8-4695-AB1B-C384781C4E7D}"/>
+    <hyperlink ref="D1351" r:id="rId1175" xr:uid="{0BA23D39-2EC1-4779-BD59-FCF86D409341}"/>
+    <hyperlink ref="D1352" r:id="rId1176" xr:uid="{9B9F80B4-017F-46A4-B16A-B8086B0AF816}"/>
+    <hyperlink ref="D1353" r:id="rId1177" xr:uid="{F436BF02-FD5A-48CF-8619-1D710BD2FFF2}"/>
+    <hyperlink ref="D1354" r:id="rId1178" xr:uid="{691E6CAB-9A70-48F0-ACD6-4812B3159BA9}"/>
+    <hyperlink ref="D1355" r:id="rId1179" xr:uid="{55A3CC84-7BA9-4B38-87BD-1BF8FD2990AC}"/>
+    <hyperlink ref="D1356" r:id="rId1180" xr:uid="{3233FFB3-8909-4586-8897-4A5B63CD4035}"/>
+    <hyperlink ref="D1357" r:id="rId1181" xr:uid="{E1E6987E-4CA7-41F0-965A-00E5F1F7E7E8}"/>
+    <hyperlink ref="D1358" r:id="rId1182" xr:uid="{E63CD818-B623-4D95-83EC-425F80837A49}"/>
+    <hyperlink ref="D1359" r:id="rId1183" xr:uid="{328E9593-65D4-41C3-BB8E-388AF80B9941}"/>
+    <hyperlink ref="D1360" r:id="rId1184" xr:uid="{134CF6C9-09B0-4BEA-8453-8549702D0C38}"/>
+    <hyperlink ref="D1361" r:id="rId1185" xr:uid="{ADF23E56-A073-4982-A40B-AAE9FD82D3F5}"/>
+    <hyperlink ref="D1362" r:id="rId1186" xr:uid="{84EC450C-37FD-4C29-BDAB-4583287CC6C6}"/>
+    <hyperlink ref="D1363" r:id="rId1187" xr:uid="{685DB31D-E6DA-4DF8-B3AB-45655937383F}"/>
+    <hyperlink ref="D1364" r:id="rId1188" xr:uid="{048D9481-DF64-40EC-8ECF-08CBC566C5F1}"/>
+    <hyperlink ref="D1365" r:id="rId1189" xr:uid="{DD907425-7425-49D7-91A4-0553AAB7D292}"/>
+    <hyperlink ref="D1366" r:id="rId1190" xr:uid="{D486ED5E-F200-4097-8611-92D51997253E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
